--- a/2026/BELTRAN 34/Agosto/Agosto BELTRAN.xlsx
+++ b/2026/BELTRAN 34/Agosto/Agosto BELTRAN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\BELTRAN 34\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BELTRAN 34\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27BA9A63-7EA8-464F-9390-B1420CE16F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF45C6E-E598-4AF9-8D75-B30726F38F42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,19 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$33</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$94</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$93</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="133">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -221,9 +226,6 @@
   </si>
   <si>
     <t>HORARIOS DE ATENCION: 10 A 15HS - LUNES A VIERNES</t>
-  </si>
-  <si>
-    <t>Seguro integral de consorcio - Sancor Seguro</t>
   </si>
   <si>
     <t>UC</t>
@@ -358,9 +360,6 @@
     <t>Matias Jose Medina Gonzalez</t>
   </si>
   <si>
-    <t xml:space="preserve">Celestino Soledad - Servicio de limpieza </t>
-  </si>
-  <si>
     <t>Ivan Aguirre - Lucia daniela Toledo</t>
   </si>
   <si>
@@ -394,46 +393,46 @@
     <t>$157.200 transfririo el 1° C. + Cochera C</t>
   </si>
   <si>
-    <t>Transf 10/07</t>
-  </si>
-  <si>
-    <t>Transf 02/07</t>
-  </si>
-  <si>
-    <t>Debito 03/07</t>
-  </si>
-  <si>
-    <t>SAC</t>
-  </si>
-  <si>
-    <t>Casa Ruan - Compra de materiales electricos - Luces de emergencia</t>
-  </si>
-  <si>
     <t>Articulos de limpieza</t>
   </si>
   <si>
-    <t>Transf 03/07</t>
-  </si>
-  <si>
-    <t>Envio carta documento local - Correo argentino</t>
-  </si>
-  <si>
     <t>Subido en Juli0 a $91.000</t>
   </si>
   <si>
     <t>VTO 17/09</t>
   </si>
   <si>
-    <t>Honorarios administracion -  JULIO - SE ADEUDA AGOSTO</t>
-  </si>
-  <si>
-    <t>Facundo Heredia - Impermeabilizacion de terraza</t>
-  </si>
-  <si>
     <t>Transf 05/08</t>
   </si>
   <si>
     <t>Transf 12/08</t>
+  </si>
+  <si>
+    <t>Celestino Soledad - Servicio de limpieza - Mes de Julio (tomo vacaciones) y Agosto</t>
+  </si>
+  <si>
+    <t>Transf 28/08</t>
+  </si>
+  <si>
+    <t>Agosto</t>
+  </si>
+  <si>
+    <t>Julio</t>
+  </si>
+  <si>
+    <t>Federacion patronal - Seguro integral de consorcio</t>
+  </si>
+  <si>
+    <t>Debito 28/08</t>
+  </si>
+  <si>
+    <t>Honorarios administracion -  JULIO Y AGOSTO</t>
+  </si>
+  <si>
+    <t>Transf 30/08</t>
+  </si>
+  <si>
+    <t>Seguro - Sra. Soledad - La Holando - Poliza nro. 690173-2</t>
   </si>
 </sst>
 </file>
@@ -959,7 +958,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="39">
+  <borders count="41">
     <border>
       <left/>
       <right/>
@@ -1421,6 +1420,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1468,7 +1489,7 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="35" applyProtection="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="36" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="186">
+  <cellXfs count="194">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1661,7 +1682,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="44" fontId="17" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1675,7 +1695,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1703,6 +1726,18 @@
     <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1718,9 +1753,6 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1751,16 +1783,27 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="8" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Énfasis1 2" xfId="4" xr:uid="{E13FD6FD-4381-40A3-9669-15D4AFB54255}"/>
@@ -1870,9 +1913,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1910,9 +1953,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1945,9 +1988,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1980,9 +2040,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2156,17 +2233,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L94"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <dimension ref="A1:L93"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" customWidth="1"/>
+    <col min="11" max="11" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2179,13 +2256,13 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="77" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B2" s="77"/>
       <c r="C2" s="77"/>
       <c r="D2" s="77"/>
     </row>
-    <row r="3" spans="1:4" ht="16.95" customHeight="1">
+    <row r="3" spans="1:4" ht="16.899999999999999" customHeight="1">
       <c r="A3" s="77" t="s">
         <v>64</v>
       </c>
@@ -2195,7 +2272,7 @@
     </row>
     <row r="4" spans="1:4" ht="32.25" customHeight="1">
       <c r="A4" s="157" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B4" s="157"/>
       <c r="C4" s="78"/>
@@ -2221,7 +2298,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="B9" s="165" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2233,7 +2310,7 @@
     <row r="13" spans="1:4" hidden="1"/>
     <row r="14" spans="1:4" ht="15" customHeight="1">
       <c r="A14" s="160" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B14" s="160"/>
       <c r="C14" s="160"/>
@@ -2258,10 +2335,10 @@
       <c r="D17" s="160"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1"/>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1">
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1">
       <c r="A19" s="1"/>
     </row>
-    <row r="20" spans="1:7" ht="15" hidden="1" thickBot="1"/>
+    <row r="20" spans="1:7" ht="15.75" hidden="1" thickBot="1"/>
     <row r="21" spans="1:7">
       <c r="A21" s="6" t="s">
         <v>21</v>
@@ -2272,7 +2349,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B22" s="15"/>
       <c r="C22" s="13"/>
@@ -2280,21 +2357,19 @@
       <c r="G22" s="22"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A23" s="54" t="s">
-        <v>109</v>
-      </c>
-      <c r="B23" s="54" t="s">
+      <c r="A23" s="189" t="s">
         <v>124</v>
       </c>
-      <c r="C23" s="146">
-        <v>131000</v>
+      <c r="B23" s="190"/>
+      <c r="C23" s="185">
+        <v>450000</v>
       </c>
       <c r="D23" s="54"/>
     </row>
-    <row r="24" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A24" s="54"/>
-      <c r="B24" s="54"/>
-      <c r="C24" s="146"/>
+    <row r="24" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A24" s="191"/>
+      <c r="B24" s="192"/>
+      <c r="C24" s="186"/>
       <c r="D24" s="54"/>
     </row>
     <row r="25" spans="1:7">
@@ -2302,9 +2377,9 @@
         <v>48</v>
       </c>
       <c r="B25" s="117"/>
-      <c r="C25" s="149">
+      <c r="C25" s="148">
         <f>SUM(C23:C24)</f>
-        <v>131000</v>
+        <v>450000</v>
       </c>
       <c r="D25" s="55"/>
     </row>
@@ -2351,7 +2426,7 @@
       <c r="C31" s="10"/>
       <c r="D31" s="56">
         <f>C25+C30</f>
-        <v>131000</v>
+        <v>450000</v>
       </c>
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
@@ -2367,27 +2442,30 @@
     </row>
     <row r="33" spans="1:7" ht="22.5" customHeight="1">
       <c r="A33" s="103" t="s">
+        <v>130</v>
+      </c>
+      <c r="B33" s="119"/>
+      <c r="C33" s="188">
+        <f>91000*2</f>
+        <v>182000</v>
+      </c>
+      <c r="D33" s="88" t="s">
         <v>131</v>
       </c>
-      <c r="B33" s="119"/>
-      <c r="C33" s="90">
-        <v>85000</v>
-      </c>
-      <c r="D33" s="88"/>
       <c r="F33" s="22" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="G33" s="9"/>
     </row>
-    <row r="34" spans="1:7" ht="15" thickBot="1">
+    <row r="34" spans="1:7" ht="15.75" thickBot="1">
       <c r="A34" s="14" t="s">
         <v>29</v>
       </c>
       <c r="B34" s="14"/>
-      <c r="C34" s="150"/>
+      <c r="C34" s="149"/>
       <c r="D34" s="56">
         <f>SUM(C33:C33)</f>
-        <v>85000</v>
+        <v>182000</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="16.5" customHeight="1">
@@ -2400,199 +2478,205 @@
     </row>
     <row r="36" spans="1:7" ht="22.5" customHeight="1">
       <c r="A36" s="158" t="s">
-        <v>65</v>
+        <v>128</v>
       </c>
       <c r="B36" s="159"/>
-      <c r="C36" s="156">
-        <v>183061</v>
+      <c r="C36" s="187">
+        <v>89533</v>
       </c>
       <c r="D36" s="87" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="15" thickBot="1">
-      <c r="A37" s="14" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="22.5" customHeight="1">
+      <c r="A37" s="154" t="s">
+        <v>132</v>
+      </c>
+      <c r="B37" s="155"/>
+      <c r="C37" s="193">
+        <v>5587.48</v>
+      </c>
+      <c r="D37" s="87" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A38" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B37" s="14"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="58">
-        <f>SUM(C36:C36)</f>
-        <v>183061</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" hidden="1">
-      <c r="A38" s="13" t="s">
+      <c r="B38" s="14"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="58">
+        <f>SUM(C36:C37)</f>
+        <v>95120.48</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" hidden="1">
+      <c r="A39" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B38" s="120"/>
-      <c r="C38" s="20"/>
-      <c r="D38" s="59"/>
-    </row>
-    <row r="39" spans="1:7" hidden="1">
-      <c r="A39" s="54" t="s">
-        <v>59</v>
-      </c>
-      <c r="B39" s="54" t="s">
-        <v>105</v>
-      </c>
-      <c r="C39" s="92"/>
-      <c r="D39" s="87"/>
-      <c r="F39" s="81"/>
+      <c r="B39" s="120"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="59"/>
     </row>
     <row r="40" spans="1:7" hidden="1">
       <c r="A40" s="54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B40" s="54" t="s">
-        <v>105</v>
-      </c>
-      <c r="C40" s="93"/>
+        <v>104</v>
+      </c>
+      <c r="C40" s="92"/>
       <c r="D40" s="87"/>
+      <c r="F40" s="81"/>
     </row>
     <row r="41" spans="1:7" hidden="1">
       <c r="A41" s="54" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B41" s="54" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C41" s="93"/>
       <c r="D41" s="87"/>
     </row>
     <row r="42" spans="1:7" hidden="1">
       <c r="A42" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="B42" s="54" t="s">
+        <v>104</v>
+      </c>
+      <c r="C42" s="93"/>
+      <c r="D42" s="87"/>
+    </row>
+    <row r="43" spans="1:7" hidden="1">
+      <c r="A43" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="B42" s="54" t="s">
-        <v>105</v>
-      </c>
-      <c r="C42" s="93"/>
-      <c r="D42" s="86"/>
-    </row>
-    <row r="43" spans="1:7" ht="15" hidden="1" customHeight="1" thickBot="1">
-      <c r="A43" s="14" t="s">
+      <c r="B43" s="54" t="s">
+        <v>104</v>
+      </c>
+      <c r="C43" s="93"/>
+      <c r="D43" s="86"/>
+    </row>
+    <row r="44" spans="1:7" ht="15" hidden="1" customHeight="1" thickBot="1">
+      <c r="A44" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B43" s="120"/>
-      <c r="C43" s="21"/>
-      <c r="D43" s="58">
-        <f>SUM(C39:C42)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44" s="13" t="s">
+      <c r="B44" s="120"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="58">
+        <f>SUM(C40:C43)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B44" s="120"/>
-      <c r="C44" s="20"/>
-      <c r="D44" s="59"/>
-    </row>
-    <row r="45" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A45" s="68" t="s">
+      <c r="B45" s="120"/>
+      <c r="C45" s="20"/>
+      <c r="D45" s="59"/>
+    </row>
+    <row r="46" spans="1:7" ht="14.25" customHeight="1">
+      <c r="A46" s="68" t="s">
+        <v>94</v>
+      </c>
+      <c r="B46" s="54"/>
+      <c r="C46" s="156">
+        <v>86429.79</v>
+      </c>
+      <c r="D46" s="85" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="14.25" customHeight="1">
+      <c r="A47" s="54" t="s">
         <v>95</v>
       </c>
-      <c r="B45" s="54"/>
-      <c r="C45" s="93">
-        <v>66292.55</v>
-      </c>
-      <c r="D45" s="85" t="s">
+      <c r="B47" s="54"/>
+      <c r="C47" s="156">
+        <v>392672.62</v>
+      </c>
+      <c r="D47" s="85" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A46" s="54" t="s">
-        <v>96</v>
-      </c>
-      <c r="B46" s="54"/>
-      <c r="C46" s="185">
-        <v>392672.62</v>
-      </c>
-      <c r="D46" s="85" t="s">
-        <v>133</v>
-      </c>
-      <c r="F46" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="15" thickBot="1">
-      <c r="A47" s="14" t="s">
+      <c r="F47" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A48" s="14" t="s">
         <v>3</v>
-      </c>
-      <c r="B47" s="14"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="58">
-        <f>SUM(C45:C46)</f>
-        <v>458965.17</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="15" thickBot="1">
-      <c r="A48" s="13" t="s">
-        <v>31</v>
       </c>
       <c r="B48" s="14"/>
       <c r="C48" s="19"/>
-      <c r="D48" s="61"/>
-    </row>
-    <row r="49" spans="1:6" ht="19.95" customHeight="1">
-      <c r="A49" s="158" t="s">
-        <v>112</v>
-      </c>
-      <c r="B49" s="159"/>
-      <c r="C49" s="185">
+      <c r="D48" s="58">
+        <f>SUM(C46:C47)</f>
+        <v>479102.41</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A49" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B49" s="14"/>
+      <c r="C49" s="19"/>
+      <c r="D49" s="61"/>
+    </row>
+    <row r="50" spans="1:6" ht="19.899999999999999" customHeight="1">
+      <c r="A50" s="158" t="s">
+        <v>110</v>
+      </c>
+      <c r="B50" s="159"/>
+      <c r="C50" s="156">
         <v>126000</v>
       </c>
-      <c r="D49" s="83" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="19.95" customHeight="1">
-      <c r="A50" s="155" t="s">
+      <c r="D50" s="83" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="19.899999999999999" customHeight="1">
+      <c r="A51" s="154" t="s">
+        <v>119</v>
+      </c>
+      <c r="B51" s="153" t="s">
+        <v>126</v>
+      </c>
+      <c r="C51" s="156">
+        <v>29400</v>
+      </c>
+      <c r="D51" s="83" t="s">
         <v>125</v>
       </c>
-      <c r="B50" s="154"/>
-      <c r="C50" s="93">
-        <v>174000</v>
-      </c>
-      <c r="D50" s="83"/>
-    </row>
-    <row r="51" spans="1:6" ht="19.95" customHeight="1">
-      <c r="A51" s="155" t="s">
-        <v>126</v>
-      </c>
-      <c r="B51" s="154"/>
-      <c r="C51" s="93">
-        <v>15500</v>
-      </c>
-      <c r="D51" s="83" t="s">
+    </row>
+    <row r="52" spans="1:6" ht="19.899999999999999" customHeight="1">
+      <c r="A52" s="154" t="s">
+        <v>119</v>
+      </c>
+      <c r="B52" s="153" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" ht="42.6" customHeight="1">
-      <c r="A52" s="158" t="s">
-        <v>132</v>
-      </c>
-      <c r="B52" s="159"/>
-      <c r="C52" s="185">
-        <v>650000</v>
+      <c r="C52" s="156">
+        <v>37600</v>
       </c>
       <c r="D52" s="83" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="15" thickBot="1">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="15.75" thickBot="1">
       <c r="A53" s="14" t="s">
         <v>11</v>
       </c>
       <c r="B53" s="13"/>
       <c r="C53" s="13"/>
       <c r="D53" s="63">
-        <f>SUM(C49:C52)</f>
-        <v>965500</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="15" thickBot="1">
+        <f>SUM(C50:C52)</f>
+        <v>193000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="15.75" thickBot="1">
       <c r="A54" s="13" t="s">
         <v>24</v>
       </c>
@@ -2602,17 +2686,17 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="54" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B55" s="54"/>
-      <c r="C55" s="93">
+      <c r="C55" s="156">
         <v>69000</v>
       </c>
       <c r="D55" s="64"/>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="54" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B56" s="54"/>
       <c r="C56" s="93">
@@ -2620,7 +2704,7 @@
       </c>
       <c r="D56" s="62"/>
     </row>
-    <row r="57" spans="1:6" ht="15" thickBot="1">
+    <row r="57" spans="1:6" ht="15.75" thickBot="1">
       <c r="A57" s="122" t="s">
         <v>29</v>
       </c>
@@ -2631,7 +2715,7 @@
         <v>109885.53</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="15" thickBot="1">
+    <row r="58" spans="1:6" ht="15.75" thickBot="1">
       <c r="A58" s="54"/>
       <c r="B58" s="54"/>
       <c r="C58" s="54"/>
@@ -2639,7 +2723,7 @@
     </row>
     <row r="59" spans="1:6" ht="20.25" customHeight="1" thickBot="1">
       <c r="A59" s="162" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B59" s="163"/>
       <c r="C59" s="164"/>
@@ -2648,14 +2732,14 @@
         <v>118436.53000000003</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="15" thickBot="1">
+    <row r="60" spans="1:6" ht="15.75" thickBot="1">
       <c r="A60" s="123"/>
       <c r="B60" s="68"/>
       <c r="C60" s="68"/>
       <c r="D60" s="69"/>
       <c r="E60" s="24"/>
     </row>
-    <row r="61" spans="1:6" ht="15" thickBot="1">
+    <row r="61" spans="1:6" ht="15.75" thickBot="1">
       <c r="A61" s="124" t="s">
         <v>25</v>
       </c>
@@ -2663,7 +2747,7 @@
       <c r="C61" s="70"/>
       <c r="D61" s="71">
         <f>(SUM(D26:D59))</f>
-        <v>2051848.23</v>
+        <v>1627544.95</v>
       </c>
       <c r="E61" s="24"/>
       <c r="F61" s="24"/>
@@ -2675,7 +2759,7 @@
       <c r="D62" s="68"/>
       <c r="F62" s="82"/>
     </row>
-    <row r="63" spans="1:6" ht="15" thickBot="1">
+    <row r="63" spans="1:6" ht="15.75" thickBot="1">
       <c r="A63" s="68"/>
       <c r="B63" s="68"/>
       <c r="C63" s="68"/>
@@ -2726,12 +2810,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="15" thickBot="1">
+    <row r="70" spans="1:4" ht="15.75" thickBot="1">
       <c r="A70" s="68"/>
       <c r="B70" s="68"/>
       <c r="C70" s="68"/>
     </row>
-    <row r="71" spans="1:4" ht="15" thickBot="1">
+    <row r="71" spans="1:4" ht="15.75" thickBot="1">
       <c r="A71" s="124" t="s">
         <v>36</v>
       </c>
@@ -2742,32 +2826,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="15" thickBot="1">
+    <row r="72" spans="1:4" ht="15.75" thickBot="1">
       <c r="A72" s="68"/>
       <c r="B72" s="68"/>
       <c r="C72" s="68"/>
     </row>
-    <row r="73" spans="1:4" ht="15" thickBot="1">
+    <row r="73" spans="1:4" ht="15.75" thickBot="1">
       <c r="A73" s="136" t="s">
         <v>26</v>
       </c>
       <c r="B73" s="137">
         <f>D61</f>
-        <v>2051848.23</v>
+        <v>1627544.95</v>
       </c>
       <c r="C73" s="138"/>
     </row>
-    <row r="74" spans="1:4" ht="15" thickBot="1">
+    <row r="74" spans="1:4" ht="15.75" thickBot="1">
       <c r="A74" s="136" t="s">
         <v>27</v>
       </c>
       <c r="B74" s="137">
         <f>D61-D59</f>
-        <v>1933411.7</v>
+        <v>1509108.42</v>
       </c>
       <c r="C74" s="68"/>
     </row>
-    <row r="75" spans="1:4" ht="15" thickBot="1">
+    <row r="75" spans="1:4" ht="15.75" thickBot="1">
       <c r="A75" s="136" t="s">
         <v>37</v>
       </c>
@@ -2777,7 +2861,7 @@
       </c>
       <c r="C75" s="68"/>
     </row>
-    <row r="76" spans="1:4" ht="15" thickBot="1">
+    <row r="76" spans="1:4" ht="15.75" thickBot="1">
       <c r="A76" s="136" t="s">
         <v>52</v>
       </c>
@@ -2792,7 +2876,7 @@
       <c r="B77" s="68"/>
       <c r="C77" s="68"/>
       <c r="D77" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2805,7 +2889,7 @@
       <c r="B79" s="68"/>
       <c r="C79" s="68"/>
     </row>
-    <row r="80" spans="1:4" ht="15" thickBot="1">
+    <row r="80" spans="1:4" ht="15.75" thickBot="1">
       <c r="A80" s="139" t="s">
         <v>47</v>
       </c>
@@ -2827,7 +2911,7 @@
       </c>
       <c r="B82" s="62">
         <f>PRORRATEO!H24</f>
-        <v>1498846.13</v>
+        <v>1194404.8999999994</v>
       </c>
       <c r="C82" s="68"/>
     </row>
@@ -2836,95 +2920,87 @@
         <v>54</v>
       </c>
       <c r="B83" s="62">
-        <f>B93</f>
+        <f>B92</f>
         <v>0</v>
       </c>
       <c r="C83" s="68"/>
     </row>
-    <row r="84" spans="1:12" ht="17.25" customHeight="1">
-      <c r="A84" s="142" t="s">
-        <v>128</v>
-      </c>
-      <c r="B84" s="151">
-        <v>-75000</v>
+    <row r="84" spans="1:12">
+      <c r="A84" s="144" t="s">
+        <v>38</v>
+      </c>
+      <c r="B84" s="150">
+        <f>-B74</f>
+        <v>-1509108.42</v>
       </c>
       <c r="C84" s="68"/>
     </row>
     <row r="85" spans="1:12">
-      <c r="A85" s="144" t="s">
-        <v>38</v>
-      </c>
-      <c r="B85" s="151">
-        <f>-B74</f>
-        <v>-1933411.7</v>
+      <c r="A85" s="143" t="s">
+        <v>39</v>
+      </c>
+      <c r="B85" s="62">
+        <f>-(B75)</f>
+        <v>0</v>
       </c>
       <c r="C85" s="68"/>
     </row>
     <row r="86" spans="1:12">
-      <c r="A86" s="143" t="s">
-        <v>39</v>
-      </c>
-      <c r="B86" s="62">
-        <f>-(B75)</f>
-        <v>0</v>
-      </c>
-      <c r="C86" s="68"/>
-    </row>
-    <row r="87" spans="1:12">
-      <c r="A87" s="11" t="s">
+      <c r="A86" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B87" s="104">
-        <f>SUM(B81:B86)</f>
-        <v>713920.24999999977</v>
-      </c>
-      <c r="C87" s="129"/>
-    </row>
-    <row r="88" spans="1:12" ht="34.5" customHeight="1">
-      <c r="B88" s="22"/>
-      <c r="C88" s="24"/>
-      <c r="D88" s="129"/>
-    </row>
-    <row r="89" spans="1:12">
-      <c r="A89" s="161" t="s">
+      <c r="B86" s="104">
+        <f>SUM(B81:B85)</f>
+        <v>908782.29999999935</v>
+      </c>
+      <c r="C86" s="129"/>
+    </row>
+    <row r="87" spans="1:12" ht="34.5" customHeight="1">
+      <c r="B87" s="22"/>
+      <c r="C87" s="24"/>
+      <c r="D87" s="129"/>
+    </row>
+    <row r="88" spans="1:12">
+      <c r="A88" s="161" t="s">
         <v>46</v>
       </c>
+      <c r="B88" s="161"/>
+    </row>
+    <row r="89" spans="1:12" ht="27.75" customHeight="1">
+      <c r="A89" s="161"/>
       <c r="B89" s="161"/>
     </row>
-    <row r="90" spans="1:12" ht="27.75" customHeight="1">
-      <c r="A90" s="161"/>
-      <c r="B90" s="161"/>
+    <row r="90" spans="1:12" ht="32.25" customHeight="1">
+      <c r="A90" s="74"/>
+      <c r="B90" s="18"/>
     </row>
     <row r="91" spans="1:12" ht="32.25" customHeight="1">
       <c r="A91" s="74"/>
       <c r="B91" s="18"/>
     </row>
-    <row r="92" spans="1:12" ht="32.25" customHeight="1">
-      <c r="A92" s="74"/>
-      <c r="B92" s="18"/>
+    <row r="92" spans="1:12">
+      <c r="A92" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B92" s="75">
+        <f>SUM(B90:B91)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="93" spans="1:12">
-      <c r="A93" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="B93" s="75">
-        <f>SUM(B91:B92)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12">
-      <c r="L94" s="4"/>
+      <c r="L93" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A4:B7"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A14:D17"/>
-    <mergeCell ref="A89:B90"/>
+    <mergeCell ref="A88:B89"/>
     <mergeCell ref="A59:C59"/>
     <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A23:B24"/>
+    <mergeCell ref="C23:C24"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2935,48 +3011,48 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:U32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5546875" customWidth="1"/>
-    <col min="3" max="3" width="4.33203125" customWidth="1"/>
-    <col min="4" max="4" width="18.44140625" customWidth="1"/>
-    <col min="5" max="5" width="13.88671875" customWidth="1"/>
-    <col min="6" max="6" width="5.109375" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" customWidth="1"/>
+    <col min="2" max="2" width="5.5703125" customWidth="1"/>
+    <col min="3" max="3" width="4.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="7.6640625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" customWidth="1"/>
-    <col min="11" max="11" width="11.109375" customWidth="1"/>
-    <col min="12" max="12" width="14.44140625" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" customWidth="1"/>
-    <col min="14" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.33203125" customWidth="1"/>
-    <col min="16" max="16" width="14.109375" customWidth="1"/>
-    <col min="17" max="17" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" customWidth="1"/>
+    <col min="14" max="14" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.28515625" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" customWidth="1"/>
+    <col min="17" max="17" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="12.9" customHeight="1">
+    <row r="1" spans="1:21" ht="12.95" customHeight="1">
       <c r="A1" s="105"/>
-      <c r="B1" s="166" t="str">
+      <c r="B1" s="170" t="str">
         <f>RESUMEN!A4</f>
         <v xml:space="preserve">Titular: CONSORCIO DE PROPIETARIOS CORONEL BELTRAN 34
 Banco Santander: Cta Corriente en Pesos 533-030591/4
 Cuit del consorcio: 30-71897608-8
 CBU: 0720533020000003059140 - Alias: SALMON.ARMADA.FOCO                                                                                                                                                                                                                                                                                                      </v>
       </c>
-      <c r="C1" s="166"/>
-      <c r="D1" s="166"/>
-      <c r="E1" s="166"/>
-      <c r="F1" s="166"/>
-      <c r="G1" s="166"/>
-      <c r="H1" s="166"/>
-      <c r="I1" s="166"/>
-      <c r="J1" s="166"/>
-      <c r="K1" s="166"/>
+      <c r="C1" s="170"/>
+      <c r="D1" s="170"/>
+      <c r="E1" s="170"/>
+      <c r="F1" s="170"/>
+      <c r="G1" s="170"/>
+      <c r="H1" s="170"/>
+      <c r="I1" s="170"/>
+      <c r="J1" s="170"/>
+      <c r="K1" s="170"/>
       <c r="L1" s="106"/>
       <c r="M1" s="106"/>
       <c r="N1" s="106"/>
@@ -2985,16 +3061,16 @@
     </row>
     <row r="2" spans="1:21" ht="33.75" customHeight="1">
       <c r="A2" s="108"/>
-      <c r="B2" s="167"/>
-      <c r="C2" s="167"/>
-      <c r="D2" s="167"/>
-      <c r="E2" s="167"/>
-      <c r="F2" s="167"/>
-      <c r="G2" s="167"/>
-      <c r="H2" s="167"/>
-      <c r="I2" s="167"/>
-      <c r="J2" s="167"/>
-      <c r="K2" s="167"/>
+      <c r="B2" s="171"/>
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="171"/>
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
+      <c r="H2" s="171"/>
+      <c r="I2" s="171"/>
+      <c r="J2" s="171"/>
+      <c r="K2" s="171"/>
       <c r="L2" s="109"/>
       <c r="M2" s="109" t="s">
         <v>4</v>
@@ -3011,118 +3087,118 @@
     </row>
     <row r="3" spans="1:21" ht="46.5" customHeight="1" thickBot="1">
       <c r="A3" s="111"/>
-      <c r="B3" s="168"/>
-      <c r="C3" s="168"/>
-      <c r="D3" s="168"/>
-      <c r="E3" s="168"/>
-      <c r="F3" s="168"/>
-      <c r="G3" s="168"/>
-      <c r="H3" s="168"/>
-      <c r="I3" s="168"/>
-      <c r="J3" s="168"/>
-      <c r="K3" s="168"/>
+      <c r="B3" s="172"/>
+      <c r="C3" s="172"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="172"/>
+      <c r="H3" s="172"/>
+      <c r="I3" s="172"/>
+      <c r="J3" s="172"/>
+      <c r="K3" s="172"/>
       <c r="L3" s="112"/>
       <c r="M3" s="112" t="s">
         <v>56</v>
       </c>
       <c r="N3" s="113"/>
-      <c r="O3" s="147">
+      <c r="O3" s="146">
         <v>0</v>
       </c>
       <c r="P3" s="114"/>
     </row>
     <row r="4" spans="1:21" ht="30.6" customHeight="1" thickBot="1">
       <c r="A4" s="3"/>
-      <c r="B4" s="179" t="s">
-        <v>98</v>
-      </c>
-      <c r="C4" s="180"/>
-      <c r="D4" s="180"/>
-      <c r="E4" s="180"/>
-      <c r="F4" s="180"/>
-      <c r="G4" s="180"/>
-      <c r="H4" s="180"/>
-      <c r="I4" s="180"/>
-      <c r="J4" s="180"/>
-      <c r="K4" s="180"/>
-      <c r="L4" s="180"/>
-      <c r="M4" s="180"/>
-      <c r="N4" s="180"/>
-      <c r="O4" s="180"/>
-      <c r="P4" s="181"/>
+      <c r="B4" s="182" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" s="183"/>
+      <c r="D4" s="183"/>
+      <c r="E4" s="183"/>
+      <c r="F4" s="183"/>
+      <c r="G4" s="183"/>
+      <c r="H4" s="183"/>
+      <c r="I4" s="183"/>
+      <c r="J4" s="183"/>
+      <c r="K4" s="183"/>
+      <c r="L4" s="183"/>
+      <c r="M4" s="183"/>
+      <c r="N4" s="183"/>
+      <c r="O4" s="183"/>
+      <c r="P4" s="184"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="182" t="s">
+      <c r="A5" s="166" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="184" t="s">
+      <c r="B5" s="168" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="171" t="s">
+      <c r="C5" s="169" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="171" t="s">
+      <c r="D5" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="171" t="s">
+      <c r="E5" s="169" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="171" t="s">
+      <c r="F5" s="169" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="171" t="s">
+      <c r="G5" s="169" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="171" t="s">
+      <c r="H5" s="169" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="171" t="s">
+      <c r="I5" s="169" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="175" t="s">
+      <c r="J5" s="178" t="s">
         <v>44</v>
       </c>
-      <c r="K5" s="173" t="s">
+      <c r="K5" s="176" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="173" t="s">
+      <c r="L5" s="176" t="s">
         <v>10</v>
       </c>
-      <c r="M5" s="173" t="s">
+      <c r="M5" s="176" t="s">
         <v>40</v>
       </c>
-      <c r="N5" s="177" t="s">
+      <c r="N5" s="180" t="s">
         <v>51</v>
       </c>
       <c r="O5" s="94" t="s">
         <v>50</v>
       </c>
-      <c r="P5" s="169" t="s">
+      <c r="P5" s="173" t="s">
         <v>49</v>
       </c>
       <c r="S5" s="24"/>
       <c r="T5" s="22"/>
     </row>
     <row r="6" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A6" s="183"/>
-      <c r="B6" s="184"/>
-      <c r="C6" s="171"/>
-      <c r="D6" s="171"/>
-      <c r="E6" s="172"/>
-      <c r="F6" s="171"/>
-      <c r="G6" s="171"/>
-      <c r="H6" s="171"/>
-      <c r="I6" s="172"/>
-      <c r="J6" s="176"/>
-      <c r="K6" s="174"/>
-      <c r="L6" s="173"/>
-      <c r="M6" s="174"/>
-      <c r="N6" s="178"/>
+      <c r="A6" s="167"/>
+      <c r="B6" s="168"/>
+      <c r="C6" s="169"/>
+      <c r="D6" s="169"/>
+      <c r="E6" s="175"/>
+      <c r="F6" s="169"/>
+      <c r="G6" s="169"/>
+      <c r="H6" s="169"/>
+      <c r="I6" s="175"/>
+      <c r="J6" s="179"/>
+      <c r="K6" s="177"/>
+      <c r="L6" s="176"/>
+      <c r="M6" s="177"/>
+      <c r="N6" s="181"/>
       <c r="O6" s="29" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 17/09</v>
       </c>
-      <c r="P6" s="169"/>
+      <c r="P6" s="173"/>
       <c r="S6" s="22">
         <v>65160</v>
       </c>
@@ -3142,27 +3218,27 @@
         <v>1</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E7" s="31"/>
       <c r="F7" s="35">
         <v>10.86</v>
       </c>
       <c r="G7" s="36">
-        <v>5037143.01</v>
-      </c>
-      <c r="H7" s="152"/>
+        <v>5442105.0099999998</v>
+      </c>
+      <c r="H7" s="151"/>
       <c r="I7" s="38"/>
       <c r="J7" s="39">
         <f>G7-H7</f>
-        <v>5037143.01</v>
+        <v>5442105.0099999998</v>
       </c>
       <c r="K7" s="39">
         <f>IF(J7&gt;0,J7*3%,0)</f>
-        <v>151114.29029999999</v>
+        <v>163263.15029999998</v>
       </c>
       <c r="L7" s="40">
         <f>O$3*F7%</f>
@@ -3177,11 +3253,11 @@
       </c>
       <c r="O7" s="42">
         <f>ROUND(SUM(J7:N7),0) + Q7</f>
-        <v>5442105.0099999998</v>
+        <v>5859216.0099999998</v>
       </c>
       <c r="P7" s="43">
         <f t="shared" ref="P7:P23" si="0">ROUND(O7*3%,0) + O7</f>
-        <v>5605368.0099999998</v>
+        <v>6034992.0099999998</v>
       </c>
       <c r="Q7" s="24">
         <v>0.01</v>
@@ -3198,37 +3274,34 @@
       </c>
     </row>
     <row r="8" spans="1:21" ht="17.100000000000001" customHeight="1">
-      <c r="A8" s="153" t="s">
+      <c r="A8" s="152" t="s">
         <v>13</v>
       </c>
       <c r="B8" s="84">
         <v>2</v>
       </c>
       <c r="C8" s="84" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D8" s="84" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E8" s="96"/>
       <c r="F8" s="35">
         <v>11.16</v>
       </c>
       <c r="G8" s="36">
-        <v>172869.02</v>
-      </c>
-      <c r="H8" s="37">
-        <f>182538.14-H18</f>
-        <v>172869.02000000002</v>
-      </c>
+        <v>183788.02</v>
+      </c>
+      <c r="H8" s="37"/>
       <c r="I8" s="38"/>
       <c r="J8" s="39">
         <f t="shared" ref="J8:J22" si="2">G8-H8</f>
-        <v>0</v>
+        <v>183788.02</v>
       </c>
       <c r="K8" s="39">
         <f t="shared" ref="K8:K22" si="3">IF(J8&gt;0,J8*3%,0)</f>
-        <v>0</v>
+        <v>5513.6405999999997</v>
       </c>
       <c r="L8" s="40">
         <f t="shared" ref="L8:L23" si="4">O$3*F8%</f>
@@ -3243,11 +3316,11 @@
       </c>
       <c r="O8" s="42">
         <f>ROUND(SUM(J8:N8),0) + Q8</f>
-        <v>183788.02</v>
+        <v>373090.02</v>
       </c>
       <c r="P8" s="43">
         <f t="shared" si="0"/>
-        <v>189302.02</v>
+        <v>384283.02</v>
       </c>
       <c r="Q8" s="24">
         <f>Q7+0.01</f>
@@ -3273,29 +3346,31 @@
         <v>4</v>
       </c>
       <c r="C9" s="84" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D9" s="95" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E9" s="84" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F9" s="97">
         <v>6.95</v>
       </c>
       <c r="G9" s="37">
-        <v>114503.03</v>
-      </c>
-      <c r="H9" s="37"/>
+        <v>232394.03</v>
+      </c>
+      <c r="H9" s="151">
+        <v>114505</v>
+      </c>
       <c r="I9" s="38"/>
       <c r="J9" s="98">
         <f t="shared" si="2"/>
-        <v>114503.03</v>
+        <v>117889.03</v>
       </c>
       <c r="K9" s="39">
         <f t="shared" si="3"/>
-        <v>3435.0908999999997</v>
+        <v>3536.6708999999996</v>
       </c>
       <c r="L9" s="99">
         <f t="shared" si="4"/>
@@ -3310,11 +3385,11 @@
       </c>
       <c r="O9" s="101">
         <f t="shared" ref="O9:O23" si="6">ROUND(SUM(J9:N9),0) + Q9</f>
-        <v>232394.03</v>
+        <v>235882.03</v>
       </c>
       <c r="P9" s="102">
         <f t="shared" si="0"/>
-        <v>239366.03</v>
+        <v>242958.03</v>
       </c>
       <c r="Q9" s="24">
         <f t="shared" ref="Q9:Q22" si="7">Q8+0.01</f>
@@ -3339,32 +3414,32 @@
         <v>3</v>
       </c>
       <c r="C10" s="84" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D10" s="84" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E10" s="84" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F10" s="35">
         <v>7.37</v>
       </c>
       <c r="G10" s="36">
-        <v>310647.03999999998</v>
-      </c>
-      <c r="H10" s="37">
-        <f>157200+129937-H20</f>
-        <v>265075.86</v>
+        <v>168311.04000000001</v>
+      </c>
+      <c r="H10" s="151">
+        <f>129937-H20</f>
+        <v>121372.86</v>
       </c>
       <c r="I10" s="38"/>
       <c r="J10" s="39">
         <f t="shared" si="2"/>
-        <v>45571.179999999993</v>
+        <v>46938.180000000008</v>
       </c>
       <c r="K10" s="39">
         <f t="shared" si="3"/>
-        <v>1367.1353999999997</v>
+        <v>1408.1454000000001</v>
       </c>
       <c r="L10" s="40">
         <f t="shared" si="4"/>
@@ -3379,11 +3454,11 @@
       </c>
       <c r="O10" s="42">
         <f t="shared" si="6"/>
-        <v>168311.04000000001</v>
+        <v>169719.04000000001</v>
       </c>
       <c r="P10" s="43">
         <f t="shared" si="0"/>
-        <v>173360.04</v>
+        <v>174811.04</v>
       </c>
       <c r="Q10" s="24">
         <f t="shared" si="7"/>
@@ -3408,27 +3483,28 @@
         <v>5</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D11" s="31" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E11" s="32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F11" s="35">
         <v>10.68</v>
       </c>
       <c r="G11" s="36">
-        <v>175883.05</v>
-      </c>
-      <c r="H11" s="37">
-        <v>181159.05</v>
+        <v>170607.05</v>
+      </c>
+      <c r="H11" s="151">
+        <f>G11</f>
+        <v>170607.05</v>
       </c>
       <c r="I11" s="38"/>
       <c r="J11" s="39">
         <f t="shared" si="2"/>
-        <v>-5276</v>
+        <v>0</v>
       </c>
       <c r="K11" s="39">
         <f t="shared" si="3"/>
@@ -3447,11 +3523,11 @@
       </c>
       <c r="O11" s="42">
         <f t="shared" si="6"/>
-        <v>170607.05</v>
+        <v>175883.05</v>
       </c>
       <c r="P11" s="43">
         <f t="shared" si="0"/>
-        <v>175725.05</v>
+        <v>181159.05</v>
       </c>
       <c r="Q11" s="24">
         <f t="shared" si="7"/>
@@ -3476,23 +3552,23 @@
         <v>7</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F12" s="35">
         <v>6.95</v>
       </c>
       <c r="G12" s="36">
-        <v>71739.06</v>
-      </c>
-      <c r="H12" s="37">
+        <v>114456.06</v>
+      </c>
+      <c r="H12" s="151">
         <f>G12</f>
-        <v>71739.06</v>
+        <v>114456.06</v>
       </c>
       <c r="I12" s="38"/>
       <c r="J12" s="39">
@@ -3545,13 +3621,13 @@
         <v>6</v>
       </c>
       <c r="C13" s="84" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D13" s="84" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E13" s="31" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F13" s="35">
         <v>6.89</v>
@@ -3559,7 +3635,7 @@
       <c r="G13" s="36">
         <v>113468.07</v>
       </c>
-      <c r="H13" s="37">
+      <c r="H13" s="151">
         <f>G13</f>
         <v>113468.07</v>
       </c>
@@ -3615,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="31" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F14" s="35">
         <v>10.68</v>
@@ -3629,7 +3705,7 @@
       <c r="G14" s="36">
         <v>175883.08</v>
       </c>
-      <c r="H14" s="37">
+      <c r="H14" s="151">
         <f>G14</f>
         <v>175883.08</v>
       </c>
@@ -3684,28 +3760,28 @@
         <v>10</v>
       </c>
       <c r="C15" s="84" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D15" s="84" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E15" s="96" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F15" s="97">
         <v>6.95</v>
       </c>
       <c r="G15" s="37">
-        <v>75188.09</v>
-      </c>
-      <c r="H15" s="37">
-        <f>G15*2</f>
-        <v>150376.18</v>
+        <v>39268.089999999997</v>
+      </c>
+      <c r="H15" s="151">
+        <f>G15</f>
+        <v>39268.089999999997</v>
       </c>
       <c r="I15" s="38"/>
       <c r="J15" s="98">
         <f t="shared" si="2"/>
-        <v>-75188.09</v>
+        <v>0</v>
       </c>
       <c r="K15" s="98">
         <v>0</v>
@@ -3723,11 +3799,11 @@
       </c>
       <c r="O15" s="101">
         <f t="shared" si="6"/>
-        <v>39268.089999999997</v>
+        <v>114456.09</v>
       </c>
       <c r="P15" s="102">
         <f t="shared" si="0"/>
-        <v>40446.089999999997</v>
+        <v>117890.09</v>
       </c>
       <c r="Q15" s="24">
         <f t="shared" si="7"/>
@@ -3752,31 +3828,31 @@
         <v>9</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F16" s="35">
         <v>6.89</v>
       </c>
       <c r="G16" s="36">
-        <v>153564.1</v>
-      </c>
-      <c r="H16" s="37">
+        <v>154767.1</v>
+      </c>
+      <c r="H16" s="151">
         <v>113468</v>
       </c>
       <c r="I16" s="38"/>
       <c r="J16" s="39">
         <f t="shared" si="2"/>
-        <v>40096.100000000006</v>
+        <v>41299.100000000006</v>
       </c>
       <c r="K16" s="39">
         <f t="shared" si="3"/>
-        <v>1202.883</v>
+        <v>1238.9730000000002</v>
       </c>
       <c r="L16" s="40">
         <f t="shared" si="4"/>
@@ -3791,18 +3867,18 @@
       </c>
       <c r="O16" s="42">
         <f t="shared" si="6"/>
-        <v>154767.1</v>
+        <v>156006.1</v>
       </c>
       <c r="P16" s="43">
         <f t="shared" si="0"/>
-        <v>159410.1</v>
+        <v>160686.1</v>
       </c>
       <c r="Q16" s="24">
         <f t="shared" si="7"/>
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="R16" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="S16" s="22">
         <v>71280</v>
@@ -3823,10 +3899,10 @@
         <v>11</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="35">
@@ -3835,7 +3911,7 @@
       <c r="G17" s="36">
         <v>195646.11</v>
       </c>
-      <c r="H17" s="37">
+      <c r="H17" s="151">
         <f>G17</f>
         <v>195646.11</v>
       </c>
@@ -3872,7 +3948,7 @@
         <v>0.10999999999999999</v>
       </c>
       <c r="R17" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="S17" s="22">
         <v>3420</v>
@@ -3890,33 +3966,30 @@
         <v>18</v>
       </c>
       <c r="B18" s="31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E18" s="32"/>
       <c r="F18" s="35">
         <v>0.56999999999999995</v>
       </c>
       <c r="G18" s="36">
-        <v>9669.1200000000008</v>
-      </c>
-      <c r="H18" s="37">
-        <f>G18</f>
-        <v>9669.1200000000008</v>
-      </c>
+        <v>9387.1200000000008</v>
+      </c>
+      <c r="H18" s="37"/>
       <c r="I18" s="38"/>
       <c r="J18" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9387.1200000000008</v>
       </c>
       <c r="K18" s="39">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>281.61360000000002</v>
       </c>
       <c r="L18" s="40">
         <f t="shared" si="4"/>
@@ -3931,11 +4004,11 @@
       </c>
       <c r="O18" s="42">
         <f t="shared" si="6"/>
-        <v>9387.1200000000008</v>
+        <v>19056.12</v>
       </c>
       <c r="P18" s="43">
         <f t="shared" si="0"/>
-        <v>9669.1200000000008</v>
+        <v>19628.12</v>
       </c>
       <c r="Q18" s="24">
         <f t="shared" si="7"/>
@@ -3957,28 +4030,28 @@
         <v>18</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C19" s="31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E19" s="32"/>
       <c r="F19" s="35">
         <v>0.52</v>
       </c>
       <c r="G19" s="36">
-        <v>8564.1299999999992</v>
-      </c>
-      <c r="H19" s="37">
-        <v>8821.1299999999992</v>
+        <v>8307.1299999999992</v>
+      </c>
+      <c r="H19" s="151">
+        <v>8556.1299999999992</v>
       </c>
       <c r="I19" s="38"/>
       <c r="J19" s="39">
         <f t="shared" si="2"/>
-        <v>-257</v>
+        <v>-249</v>
       </c>
       <c r="K19" s="39">
         <f t="shared" si="3"/>
@@ -3997,11 +4070,11 @@
       </c>
       <c r="O19" s="42">
         <f t="shared" si="6"/>
-        <v>8307.1299999999992</v>
+        <v>8315.1299999999992</v>
       </c>
       <c r="P19" s="43">
         <f t="shared" si="0"/>
-        <v>8556.1299999999992</v>
+        <v>8564.1299999999992</v>
       </c>
       <c r="Q19" s="24">
         <f t="shared" si="7"/>
@@ -4023,26 +4096,26 @@
         <v>19</v>
       </c>
       <c r="B20" s="31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C20" s="31" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E20" s="31" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F20" s="35">
         <v>0.52</v>
       </c>
       <c r="G20" s="36">
-        <v>22061.14</v>
-      </c>
-      <c r="H20" s="37">
+        <v>8564.14</v>
+      </c>
+      <c r="H20" s="151">
         <f>G20</f>
-        <v>22061.14</v>
+        <v>8564.14</v>
       </c>
       <c r="I20" s="38"/>
       <c r="J20" s="39">
@@ -4092,13 +4165,13 @@
         <v>19</v>
       </c>
       <c r="B21" s="31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C21" s="31" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E21" s="32"/>
       <c r="F21" s="35">
@@ -4107,7 +4180,7 @@
       <c r="G21" s="36">
         <v>8564.15</v>
       </c>
-      <c r="H21" s="37">
+      <c r="H21" s="151">
         <f>G21</f>
         <v>8564.15</v>
       </c>
@@ -4159,13 +4232,13 @@
         <v>20</v>
       </c>
       <c r="B22" s="31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C22" s="31" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E22" s="31"/>
       <c r="F22" s="35">
@@ -4174,7 +4247,7 @@
       <c r="G22" s="36">
         <v>10046.16</v>
       </c>
-      <c r="H22" s="37">
+      <c r="H22" s="151">
         <f>G22</f>
         <v>10046.16</v>
       </c>
@@ -4269,11 +4342,11 @@
       </c>
       <c r="G24" s="27">
         <f>SUM(G7:G23)</f>
-        <v>6655438.3599999994</v>
+        <v>7035562.3599999994</v>
       </c>
       <c r="H24" s="30">
         <f>SUM(H7:H23)</f>
-        <v>1498846.13</v>
+        <v>1194404.8999999994</v>
       </c>
       <c r="I24" s="30">
         <f>SUM(I7:I23)</f>
@@ -4295,11 +4368,11 @@
       </c>
       <c r="O24" s="53">
         <f>SUM(O7:O22)</f>
-        <v>7035562.3599999994</v>
+        <v>7738251.3599999994</v>
       </c>
       <c r="P24" s="53">
         <f>SUM(P7:P22)</f>
-        <v>7246628.3599999994</v>
+        <v>7970397.3599999994</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="12.75" customHeight="1">
@@ -4309,99 +4382,94 @@
     </row>
     <row r="26" spans="1:21" ht="15" hidden="1" customHeight="1"/>
     <row r="27" spans="1:21" ht="15" customHeight="1">
-      <c r="D27" s="170" t="s">
+      <c r="D27" s="174" t="s">
         <v>63</v>
       </c>
-      <c r="E27" s="170"/>
-      <c r="F27" s="170"/>
-      <c r="G27" s="170"/>
-      <c r="H27" s="170"/>
-      <c r="I27" s="170"/>
-      <c r="J27" s="170"/>
-      <c r="K27" s="170"/>
-      <c r="L27" s="170"/>
-      <c r="M27" s="170"/>
-      <c r="N27" s="170"/>
-      <c r="O27" s="170"/>
+      <c r="E27" s="174"/>
+      <c r="F27" s="174"/>
+      <c r="G27" s="174"/>
+      <c r="H27" s="174"/>
+      <c r="I27" s="174"/>
+      <c r="J27" s="174"/>
+      <c r="K27" s="174"/>
+      <c r="L27" s="174"/>
+      <c r="M27" s="174"/>
+      <c r="N27" s="174"/>
+      <c r="O27" s="174"/>
       <c r="S27" s="22"/>
     </row>
     <row r="28" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D28" s="170"/>
-      <c r="E28" s="170"/>
-      <c r="F28" s="170"/>
-      <c r="G28" s="170"/>
-      <c r="H28" s="170"/>
-      <c r="I28" s="170"/>
-      <c r="J28" s="170"/>
-      <c r="K28" s="170"/>
-      <c r="L28" s="170"/>
-      <c r="M28" s="170"/>
-      <c r="N28" s="170"/>
-      <c r="O28" s="170"/>
+      <c r="D28" s="174"/>
+      <c r="E28" s="174"/>
+      <c r="F28" s="174"/>
+      <c r="G28" s="174"/>
+      <c r="H28" s="174"/>
+      <c r="I28" s="174"/>
+      <c r="J28" s="174"/>
+      <c r="K28" s="174"/>
+      <c r="L28" s="174"/>
+      <c r="M28" s="174"/>
+      <c r="N28" s="174"/>
+      <c r="O28" s="174"/>
     </row>
     <row r="29" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D29" s="170"/>
-      <c r="E29" s="170"/>
-      <c r="F29" s="170"/>
-      <c r="G29" s="170"/>
-      <c r="H29" s="170"/>
-      <c r="I29" s="170"/>
-      <c r="J29" s="170"/>
-      <c r="K29" s="170"/>
-      <c r="L29" s="170"/>
-      <c r="M29" s="170"/>
-      <c r="N29" s="170"/>
-      <c r="O29" s="170"/>
+      <c r="D29" s="174"/>
+      <c r="E29" s="174"/>
+      <c r="F29" s="174"/>
+      <c r="G29" s="174"/>
+      <c r="H29" s="174"/>
+      <c r="I29" s="174"/>
+      <c r="J29" s="174"/>
+      <c r="K29" s="174"/>
+      <c r="L29" s="174"/>
+      <c r="M29" s="174"/>
+      <c r="N29" s="174"/>
+      <c r="O29" s="174"/>
     </row>
     <row r="30" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D30" s="170"/>
-      <c r="E30" s="170"/>
-      <c r="F30" s="170"/>
-      <c r="G30" s="170"/>
-      <c r="H30" s="170"/>
-      <c r="I30" s="170"/>
-      <c r="J30" s="170"/>
-      <c r="K30" s="170"/>
-      <c r="L30" s="170"/>
-      <c r="M30" s="170"/>
-      <c r="N30" s="170"/>
-      <c r="O30" s="170"/>
+      <c r="D30" s="174"/>
+      <c r="E30" s="174"/>
+      <c r="F30" s="174"/>
+      <c r="G30" s="174"/>
+      <c r="H30" s="174"/>
+      <c r="I30" s="174"/>
+      <c r="J30" s="174"/>
+      <c r="K30" s="174"/>
+      <c r="L30" s="174"/>
+      <c r="M30" s="174"/>
+      <c r="N30" s="174"/>
+      <c r="O30" s="174"/>
     </row>
     <row r="31" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D31" s="170"/>
-      <c r="E31" s="170"/>
-      <c r="F31" s="170"/>
-      <c r="G31" s="170"/>
-      <c r="H31" s="170"/>
-      <c r="I31" s="170"/>
-      <c r="J31" s="170"/>
-      <c r="K31" s="170"/>
-      <c r="L31" s="170"/>
-      <c r="M31" s="170"/>
-      <c r="N31" s="170"/>
-      <c r="O31" s="170"/>
+      <c r="D31" s="174"/>
+      <c r="E31" s="174"/>
+      <c r="F31" s="174"/>
+      <c r="G31" s="174"/>
+      <c r="H31" s="174"/>
+      <c r="I31" s="174"/>
+      <c r="J31" s="174"/>
+      <c r="K31" s="174"/>
+      <c r="L31" s="174"/>
+      <c r="M31" s="174"/>
+      <c r="N31" s="174"/>
+      <c r="O31" s="174"/>
     </row>
     <row r="32" spans="1:21" ht="65.25" customHeight="1">
-      <c r="D32" s="170"/>
-      <c r="E32" s="170"/>
-      <c r="F32" s="170"/>
-      <c r="G32" s="170"/>
-      <c r="H32" s="170"/>
-      <c r="I32" s="170"/>
-      <c r="J32" s="170"/>
-      <c r="K32" s="170"/>
-      <c r="L32" s="170"/>
-      <c r="M32" s="170"/>
-      <c r="N32" s="170"/>
-      <c r="O32" s="170"/>
+      <c r="D32" s="174"/>
+      <c r="E32" s="174"/>
+      <c r="F32" s="174"/>
+      <c r="G32" s="174"/>
+      <c r="H32" s="174"/>
+      <c r="I32" s="174"/>
+      <c r="J32" s="174"/>
+      <c r="K32" s="174"/>
+      <c r="L32" s="174"/>
+      <c r="M32" s="174"/>
+      <c r="N32" s="174"/>
+      <c r="O32" s="174"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="F5:F6"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P5:P6"/>
     <mergeCell ref="D27:O32"/>
@@ -4415,6 +4483,11 @@
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="B4:P4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="F5:F6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" orientation="landscape" r:id="rId1"/>
@@ -4424,11 +4497,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA3CC01E-5816-4D6D-A47C-EE31C4411A86}">
   <dimension ref="C3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="3" spans="3:3">
-      <c r="C3" s="148" t="s">
-        <v>120</v>
+      <c r="C3" s="147" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/2026/BELTRAN 34/Agosto/Agosto BELTRAN.xlsx
+++ b/2026/BELTRAN 34/Agosto/Agosto BELTRAN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BELTRAN 34\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF45C6E-E598-4AF9-8D75-B30726F38F42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{194BC290-6F03-4F6D-A6B9-40857D8D3308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="134">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -433,6 +433,9 @@
   </si>
   <si>
     <t>Seguro - Sra. Soledad - La Holando - Poliza nro. 690173-2</t>
+  </si>
+  <si>
+    <t>Hay una diferencia de caja correspondiente a un gasto de AYSA a solucionar en S3ptiembr3</t>
   </si>
 </sst>
 </file>
@@ -448,7 +451,7 @@
     <numFmt numFmtId="166" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="44">
+  <fonts count="42">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -531,16 +534,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <i/>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -556,14 +549,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -745,8 +730,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color rgb="FFFF0000"/>
+      <b/>
+      <sz val="12"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1447,65 +1432,59 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="29" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="30" applyProtection="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="31" applyProtection="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="29" applyProtection="0"/>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="23" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="32" fillId="32" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="33" fillId="33" borderId="32" applyProtection="0"/>
-    <xf numFmtId="0" fontId="34" fillId="26" borderId="33" applyProtection="0"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="29" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="30" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="31" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="29" applyProtection="0"/>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="31" fillId="33" borderId="32" applyProtection="0"/>
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="33" applyProtection="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="34" applyProtection="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="35" applyProtection="0"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="36" applyProtection="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="34" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="35" applyProtection="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="36" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="194">
+  <cellXfs count="185">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="8" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
@@ -1516,60 +1495,60 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="13" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="17" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="12" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="15" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="9" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="5" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="13" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="19" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="19" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="19" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="12" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="17" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="13" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="12" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="9" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="18" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="9" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="19" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="44" fontId="9" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="19" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="9" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="19" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="6" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="9" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="9" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1591,16 +1570,16 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="13" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="5" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1608,23 +1587,23 @@
     <xf numFmtId="8" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="13" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="12" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1643,8 +1622,8 @@
     </xf>
     <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1656,7 +1635,7 @@
     <xf numFmtId="10" fontId="6" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1673,7 +1652,7 @@
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="9" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="41" fillId="2" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="39" fillId="2" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1684,47 +1663,99 @@
     <xf numFmtId="44" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="17" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="15" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="6" fillId="4" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="42" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="43" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="40" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1732,78 +1763,21 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="8" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Énfasis1 2" xfId="4" xr:uid="{E13FD6FD-4381-40A3-9669-15D4AFB54255}"/>
@@ -2247,359 +2221,383 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="74" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="77" t="s">
+      <c r="A2" s="71" t="s">
         <v>93</v>
       </c>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
     </row>
     <row r="3" spans="1:4" ht="16.899999999999999" customHeight="1">
-      <c r="A3" s="77" t="s">
+      <c r="A3" s="71" t="s">
         <v>64</v>
       </c>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
     </row>
     <row r="4" spans="1:4" ht="32.25" customHeight="1">
-      <c r="A4" s="157" t="s">
+      <c r="A4" s="148" t="s">
         <v>103</v>
       </c>
-      <c r="B4" s="157"/>
-      <c r="C4" s="78"/>
-      <c r="D4" s="78"/>
+      <c r="B4" s="148"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="157"/>
-      <c r="B5" s="157"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
+      <c r="A5" s="148"/>
+      <c r="B5" s="148"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="157"/>
-      <c r="B6" s="157"/>
-      <c r="C6" s="78"/>
-      <c r="D6" s="78"/>
+      <c r="A6" s="148"/>
+      <c r="B6" s="148"/>
+      <c r="C6" s="72"/>
+      <c r="D6" s="72"/>
     </row>
     <row r="7" spans="1:4" ht="13.5" customHeight="1">
-      <c r="A7" s="157"/>
-      <c r="B7" s="157"/>
-      <c r="C7" s="78"/>
-      <c r="D7" s="78"/>
+      <c r="A7" s="148"/>
+      <c r="B7" s="148"/>
+      <c r="C7" s="72"/>
+      <c r="D7" s="72"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="B9" s="165" t="s">
+      <c r="B9" s="155" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="B10" s="165"/>
+      <c r="B10" s="155"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="B11" s="165"/>
-    </row>
-    <row r="13" spans="1:4" hidden="1"/>
+      <c r="B11" s="155"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="62"/>
+      <c r="B12" s="62"/>
+      <c r="C12" s="62"/>
+      <c r="D12" s="62"/>
+    </row>
+    <row r="13" spans="1:4" hidden="1">
+      <c r="A13" s="62"/>
+      <c r="B13" s="62"/>
+      <c r="C13" s="62"/>
+      <c r="D13" s="62"/>
+    </row>
     <row r="14" spans="1:4" ht="15" customHeight="1">
-      <c r="A14" s="160" t="s">
+      <c r="A14" s="179" t="s">
         <v>96</v>
       </c>
-      <c r="B14" s="160"/>
-      <c r="C14" s="160"/>
-      <c r="D14" s="160"/>
+      <c r="B14" s="179"/>
+      <c r="C14" s="179"/>
+      <c r="D14" s="179"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1">
-      <c r="A15" s="160"/>
-      <c r="B15" s="160"/>
-      <c r="C15" s="160"/>
-      <c r="D15" s="160"/>
+      <c r="A15" s="179"/>
+      <c r="B15" s="179"/>
+      <c r="C15" s="179"/>
+      <c r="D15" s="179"/>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1">
-      <c r="A16" s="160"/>
-      <c r="B16" s="160"/>
-      <c r="C16" s="160"/>
-      <c r="D16" s="160"/>
+      <c r="A16" s="179"/>
+      <c r="B16" s="179"/>
+      <c r="C16" s="179"/>
+      <c r="D16" s="179"/>
     </row>
     <row r="17" spans="1:7" ht="53.25" customHeight="1">
-      <c r="A17" s="160"/>
-      <c r="B17" s="160"/>
-      <c r="C17" s="160"/>
-      <c r="D17" s="160"/>
-    </row>
-    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1"/>
+      <c r="A17" s="179"/>
+      <c r="B17" s="179"/>
+      <c r="C17" s="179"/>
+      <c r="D17" s="179"/>
+    </row>
+    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A18" s="62"/>
+      <c r="B18" s="62"/>
+      <c r="C18" s="62"/>
+      <c r="D18" s="62"/>
+    </row>
     <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1">
-      <c r="A19" s="1"/>
-    </row>
-    <row r="20" spans="1:7" ht="15.75" hidden="1" thickBot="1"/>
+      <c r="A19" s="180"/>
+      <c r="B19" s="62"/>
+      <c r="C19" s="62"/>
+      <c r="D19" s="62"/>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" hidden="1" thickBot="1">
+      <c r="A20" s="62"/>
+      <c r="B20" s="62"/>
+      <c r="C20" s="62"/>
+      <c r="D20" s="62"/>
+    </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="120" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="8"/>
+      <c r="B21" s="121"/>
+      <c r="C21" s="66"/>
+      <c r="D21" s="67"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="G22" s="22"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="G22" s="16"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A23" s="189" t="s">
+      <c r="A23" s="156" t="s">
         <v>124</v>
       </c>
-      <c r="B23" s="190"/>
-      <c r="C23" s="185">
+      <c r="B23" s="157"/>
+      <c r="C23" s="181">
         <v>450000</v>
       </c>
-      <c r="D23" s="54"/>
+      <c r="D23" s="48"/>
     </row>
     <row r="24" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A24" s="191"/>
-      <c r="B24" s="192"/>
-      <c r="C24" s="186"/>
-      <c r="D24" s="54"/>
+      <c r="A24" s="158"/>
+      <c r="B24" s="159"/>
+      <c r="C24" s="182"/>
+      <c r="D24" s="48"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="117" t="s">
+      <c r="A25" s="111" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="117"/>
-      <c r="C25" s="148">
+      <c r="B25" s="111"/>
+      <c r="C25" s="142">
         <f>SUM(C23:C24)</f>
         <v>450000</v>
       </c>
-      <c r="D25" s="55"/>
+      <c r="D25" s="49"/>
     </row>
     <row r="26" spans="1:7" ht="0.6" customHeight="1">
-      <c r="A26" s="54"/>
-      <c r="B26" s="54"/>
-      <c r="C26" s="90"/>
-      <c r="D26" s="79"/>
+      <c r="A26" s="48"/>
+      <c r="B26" s="48"/>
+      <c r="C26" s="84"/>
+      <c r="D26" s="73"/>
     </row>
     <row r="27" spans="1:7" hidden="1">
-      <c r="A27" s="54"/>
-      <c r="B27" s="54"/>
-      <c r="C27" s="90"/>
-      <c r="D27" s="79"/>
+      <c r="A27" s="48"/>
+      <c r="B27" s="48"/>
+      <c r="C27" s="84"/>
+      <c r="D27" s="73"/>
     </row>
     <row r="28" spans="1:7" hidden="1">
-      <c r="A28" s="54"/>
-      <c r="B28" s="54"/>
-      <c r="C28" s="90"/>
-      <c r="D28" s="79"/>
+      <c r="A28" s="48"/>
+      <c r="B28" s="48"/>
+      <c r="C28" s="84"/>
+      <c r="D28" s="73"/>
     </row>
     <row r="29" spans="1:7" hidden="1">
-      <c r="A29" s="54"/>
-      <c r="B29" s="54"/>
-      <c r="C29" s="91"/>
-      <c r="D29" s="79"/>
+      <c r="A29" s="48"/>
+      <c r="B29" s="48"/>
+      <c r="C29" s="85"/>
+      <c r="D29" s="73"/>
     </row>
     <row r="30" spans="1:7" hidden="1">
-      <c r="A30" s="117" t="s">
+      <c r="A30" s="111" t="s">
         <v>48</v>
       </c>
-      <c r="B30" s="118"/>
-      <c r="C30" s="28">
+      <c r="B30" s="112"/>
+      <c r="C30" s="22">
         <f>SUM(C26:C29)</f>
         <v>0</v>
       </c>
-      <c r="D30" s="55"/>
+      <c r="D30" s="49"/>
     </row>
     <row r="31" spans="1:7" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A31" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B31" s="14"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="56">
+      <c r="A31" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" s="9"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="50">
         <f>C25+C30</f>
         <v>450000</v>
       </c>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="13" t="s">
+      <c r="A32" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B32" s="13"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="57"/>
-      <c r="F32" s="9"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="51"/>
+      <c r="F32" s="4"/>
     </row>
     <row r="33" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A33" s="103" t="s">
+      <c r="A33" s="97" t="s">
         <v>130</v>
       </c>
-      <c r="B33" s="119"/>
-      <c r="C33" s="188">
+      <c r="B33" s="113"/>
+      <c r="C33" s="84">
         <f>91000*2</f>
         <v>182000</v>
       </c>
-      <c r="D33" s="88" t="s">
+      <c r="D33" s="82" t="s">
         <v>131</v>
       </c>
-      <c r="F33" s="22" t="s">
+      <c r="F33" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="G33" s="9"/>
+      <c r="G33" s="4"/>
     </row>
     <row r="34" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A34" s="14" t="s">
+      <c r="A34" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B34" s="14"/>
-      <c r="C34" s="149"/>
-      <c r="D34" s="56">
+      <c r="B34" s="9"/>
+      <c r="C34" s="143"/>
+      <c r="D34" s="50">
         <f>SUM(C33:C33)</f>
         <v>182000</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="16.5" customHeight="1">
-      <c r="A35" s="13" t="s">
+      <c r="A35" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B35" s="14"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="33"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="27"/>
     </row>
     <row r="36" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A36" s="158" t="s">
+      <c r="A36" s="149" t="s">
         <v>128</v>
       </c>
-      <c r="B36" s="159"/>
-      <c r="C36" s="187">
+      <c r="B36" s="150"/>
+      <c r="C36" s="183">
         <v>89533</v>
       </c>
-      <c r="D36" s="87" t="s">
+      <c r="D36" s="81" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A37" s="154" t="s">
+      <c r="A37" s="146" t="s">
         <v>132</v>
       </c>
-      <c r="B37" s="155"/>
-      <c r="C37" s="193">
+      <c r="B37" s="147"/>
+      <c r="C37" s="184">
         <v>5587.48</v>
       </c>
-      <c r="D37" s="87" t="s">
+      <c r="D37" s="81" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A38" s="14" t="s">
+      <c r="A38" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B38" s="14"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="58">
+      <c r="B38" s="9"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="52">
         <f>SUM(C36:C37)</f>
         <v>95120.48</v>
       </c>
     </row>
     <row r="39" spans="1:7" hidden="1">
-      <c r="A39" s="13" t="s">
+      <c r="A39" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B39" s="120"/>
-      <c r="C39" s="20"/>
-      <c r="D39" s="59"/>
+      <c r="B39" s="114"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="53"/>
     </row>
     <row r="40" spans="1:7" hidden="1">
-      <c r="A40" s="54" t="s">
+      <c r="A40" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="B40" s="54" t="s">
+      <c r="B40" s="48" t="s">
         <v>104</v>
       </c>
-      <c r="C40" s="92"/>
-      <c r="D40" s="87"/>
-      <c r="F40" s="81"/>
+      <c r="C40" s="86"/>
+      <c r="D40" s="81"/>
+      <c r="F40" s="75"/>
     </row>
     <row r="41" spans="1:7" hidden="1">
-      <c r="A41" s="54" t="s">
+      <c r="A41" s="48" t="s">
         <v>60</v>
       </c>
-      <c r="B41" s="54" t="s">
+      <c r="B41" s="48" t="s">
         <v>104</v>
       </c>
-      <c r="C41" s="93"/>
-      <c r="D41" s="87"/>
+      <c r="C41" s="87"/>
+      <c r="D41" s="81"/>
     </row>
     <row r="42" spans="1:7" hidden="1">
-      <c r="A42" s="54" t="s">
+      <c r="A42" s="48" t="s">
         <v>61</v>
       </c>
-      <c r="B42" s="54" t="s">
+      <c r="B42" s="48" t="s">
         <v>104</v>
       </c>
-      <c r="C42" s="93"/>
-      <c r="D42" s="87"/>
+      <c r="C42" s="87"/>
+      <c r="D42" s="81"/>
     </row>
     <row r="43" spans="1:7" hidden="1">
-      <c r="A43" s="54" t="s">
+      <c r="A43" s="48" t="s">
         <v>62</v>
       </c>
-      <c r="B43" s="54" t="s">
+      <c r="B43" s="48" t="s">
         <v>104</v>
       </c>
-      <c r="C43" s="93"/>
-      <c r="D43" s="86"/>
+      <c r="C43" s="87"/>
+      <c r="D43" s="80"/>
     </row>
     <row r="44" spans="1:7" ht="15" hidden="1" customHeight="1" thickBot="1">
-      <c r="A44" s="14" t="s">
+      <c r="A44" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B44" s="120"/>
-      <c r="C44" s="21"/>
-      <c r="D44" s="58">
+      <c r="B44" s="114"/>
+      <c r="C44" s="15"/>
+      <c r="D44" s="52">
         <f>SUM(C40:C43)</f>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="13" t="s">
+      <c r="A45" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B45" s="120"/>
-      <c r="C45" s="20"/>
-      <c r="D45" s="59"/>
+      <c r="B45" s="114"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="53"/>
     </row>
     <row r="46" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A46" s="68" t="s">
+      <c r="A46" s="62" t="s">
         <v>94</v>
       </c>
-      <c r="B46" s="54"/>
-      <c r="C46" s="156">
+      <c r="B46" s="48"/>
+      <c r="C46" s="87">
         <v>86429.79</v>
       </c>
-      <c r="D46" s="85" t="s">
+      <c r="D46" s="79" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A47" s="54" t="s">
+      <c r="A47" s="48" t="s">
         <v>95</v>
       </c>
-      <c r="B47" s="54"/>
-      <c r="C47" s="156">
+      <c r="B47" s="48"/>
+      <c r="C47" s="87">
         <v>392672.62</v>
       </c>
-      <c r="D47" s="85" t="s">
+      <c r="D47" s="79" t="s">
         <v>122</v>
       </c>
       <c r="F47" t="s">
@@ -2607,388 +2605,390 @@
       </c>
     </row>
     <row r="48" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A48" s="14" t="s">
+      <c r="A48" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B48" s="14"/>
-      <c r="C48" s="19"/>
-      <c r="D48" s="58">
+      <c r="B48" s="9"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="52">
         <f>SUM(C46:C47)</f>
         <v>479102.41</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A49" s="13" t="s">
+      <c r="A49" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B49" s="14"/>
-      <c r="C49" s="19"/>
-      <c r="D49" s="61"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="13"/>
+      <c r="D49" s="55"/>
     </row>
     <row r="50" spans="1:6" ht="19.899999999999999" customHeight="1">
-      <c r="A50" s="158" t="s">
+      <c r="A50" s="149" t="s">
         <v>110</v>
       </c>
-      <c r="B50" s="159"/>
-      <c r="C50" s="156">
+      <c r="B50" s="150"/>
+      <c r="C50" s="87">
         <v>126000</v>
       </c>
-      <c r="D50" s="83" t="s">
+      <c r="D50" s="77" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="19.899999999999999" customHeight="1">
-      <c r="A51" s="154" t="s">
+      <c r="A51" s="146" t="s">
         <v>119</v>
       </c>
-      <c r="B51" s="153" t="s">
+      <c r="B51" s="147" t="s">
         <v>126</v>
       </c>
-      <c r="C51" s="156">
+      <c r="C51" s="87">
         <v>29400</v>
       </c>
-      <c r="D51" s="83" t="s">
+      <c r="D51" s="77" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="19.899999999999999" customHeight="1">
-      <c r="A52" s="154" t="s">
+      <c r="A52" s="146" t="s">
         <v>119</v>
       </c>
-      <c r="B52" s="153" t="s">
+      <c r="B52" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="C52" s="156">
+      <c r="C52" s="87">
         <v>37600</v>
       </c>
-      <c r="D52" s="83" t="s">
+      <c r="D52" s="77" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A53" s="14" t="s">
+      <c r="A53" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B53" s="13"/>
-      <c r="C53" s="13"/>
-      <c r="D53" s="63">
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="57">
         <f>SUM(C50:C52)</f>
         <v>193000</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A54" s="13" t="s">
+      <c r="A54" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B54" s="121"/>
-      <c r="C54" s="10"/>
-      <c r="D54" s="61"/>
+      <c r="B54" s="115"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="55"/>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="54" t="s">
+      <c r="A55" s="48" t="s">
         <v>117</v>
       </c>
-      <c r="B55" s="54"/>
-      <c r="C55" s="156">
+      <c r="B55" s="48"/>
+      <c r="C55" s="87">
         <v>69000</v>
       </c>
-      <c r="D55" s="64"/>
+      <c r="D55" s="58"/>
     </row>
     <row r="56" spans="1:6">
-      <c r="A56" s="54" t="s">
+      <c r="A56" s="48" t="s">
         <v>102</v>
       </c>
-      <c r="B56" s="54"/>
-      <c r="C56" s="93">
-        <v>40885.53</v>
-      </c>
-      <c r="D56" s="62"/>
+      <c r="B56" s="48"/>
+      <c r="C56" s="87">
+        <v>40355.57</v>
+      </c>
+      <c r="D56" s="56"/>
     </row>
     <row r="57" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A57" s="122" t="s">
+      <c r="A57" s="116" t="s">
         <v>29</v>
       </c>
-      <c r="B57" s="122"/>
-      <c r="C57" s="65"/>
-      <c r="D57" s="58">
+      <c r="B57" s="116"/>
+      <c r="C57" s="59"/>
+      <c r="D57" s="52">
         <f>SUM(C55:C56)</f>
-        <v>109885.53</v>
+        <v>109355.57</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A58" s="54"/>
-      <c r="B58" s="54"/>
-      <c r="C58" s="54"/>
-      <c r="D58" s="66"/>
+      <c r="A58" s="48"/>
+      <c r="B58" s="48"/>
+      <c r="C58" s="48"/>
+      <c r="D58" s="60"/>
     </row>
     <row r="59" spans="1:6" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A59" s="162" t="s">
+      <c r="A59" s="152" t="s">
         <v>114</v>
       </c>
-      <c r="B59" s="163"/>
-      <c r="C59" s="164"/>
-      <c r="D59" s="67">
-        <f>1646848.23-1528411.7</f>
-        <v>118436.53000000003</v>
+      <c r="B59" s="153"/>
+      <c r="C59" s="154"/>
+      <c r="D59" s="61">
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A60" s="123"/>
-      <c r="B60" s="68"/>
-      <c r="C60" s="68"/>
-      <c r="D60" s="69"/>
-      <c r="E60" s="24"/>
+      <c r="A60" s="117"/>
+      <c r="B60" s="62"/>
+      <c r="C60" s="62"/>
+      <c r="D60" s="63"/>
+      <c r="E60" s="18"/>
     </row>
     <row r="61" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A61" s="124" t="s">
+      <c r="A61" s="118" t="s">
         <v>25</v>
       </c>
-      <c r="B61" s="125"/>
-      <c r="C61" s="70"/>
-      <c r="D61" s="71">
+      <c r="B61" s="119"/>
+      <c r="C61" s="64"/>
+      <c r="D61" s="65">
         <f>(SUM(D26:D59))</f>
-        <v>1627544.95</v>
-      </c>
-      <c r="E61" s="24"/>
-      <c r="F61" s="24"/>
+        <v>1508578.46</v>
+      </c>
+      <c r="E61" s="18"/>
+      <c r="F61" s="18"/>
     </row>
     <row r="62" spans="1:6">
-      <c r="A62" s="68"/>
-      <c r="B62" s="68"/>
-      <c r="C62" s="68"/>
-      <c r="D62" s="68"/>
-      <c r="F62" s="82"/>
+      <c r="A62" s="62"/>
+      <c r="B62" s="62"/>
+      <c r="C62" s="62"/>
+      <c r="D62" s="62"/>
+      <c r="F62" s="76"/>
     </row>
     <row r="63" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A63" s="68"/>
-      <c r="B63" s="68"/>
-      <c r="C63" s="68"/>
-      <c r="D63" s="68"/>
+      <c r="A63" s="62"/>
+      <c r="B63" s="62"/>
+      <c r="C63" s="62"/>
+      <c r="D63" s="62"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="A64" s="126" t="s">
+      <c r="A64" s="120" t="s">
         <v>34</v>
       </c>
-      <c r="B64" s="127"/>
-      <c r="C64" s="72"/>
-      <c r="D64" s="73"/>
+      <c r="B64" s="121"/>
+      <c r="C64" s="66"/>
+      <c r="D64" s="67"/>
     </row>
     <row r="65" spans="1:4">
-      <c r="A65" s="130"/>
-      <c r="B65" s="131"/>
-      <c r="C65" s="93"/>
-      <c r="D65" s="60"/>
+      <c r="A65" s="124"/>
+      <c r="B65" s="125"/>
+      <c r="C65" s="87"/>
+      <c r="D65" s="54"/>
     </row>
     <row r="66" spans="1:4">
-      <c r="A66" s="122" t="s">
+      <c r="A66" s="116" t="s">
         <v>29</v>
       </c>
-      <c r="B66" s="132"/>
-      <c r="C66" s="133"/>
-      <c r="D66" s="145">
+      <c r="B66" s="126"/>
+      <c r="C66" s="127"/>
+      <c r="D66" s="139">
         <f>SUM(C65:C65)</f>
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="15" customHeight="1">
-      <c r="A67" s="68"/>
-      <c r="B67" s="68"/>
-      <c r="C67" s="68"/>
+      <c r="A67" s="62"/>
+      <c r="B67" s="62"/>
+      <c r="C67" s="62"/>
     </row>
     <row r="68" spans="1:4" hidden="1">
-      <c r="A68" s="68"/>
-      <c r="B68" s="68"/>
-      <c r="C68" s="68"/>
+      <c r="A68" s="62"/>
+      <c r="B68" s="62"/>
+      <c r="C68" s="62"/>
     </row>
     <row r="69" spans="1:4">
-      <c r="A69" s="134" t="s">
+      <c r="A69" s="128" t="s">
         <v>35</v>
       </c>
-      <c r="B69" s="134"/>
-      <c r="C69" s="135"/>
-      <c r="D69" s="89">
+      <c r="B69" s="128"/>
+      <c r="C69" s="129"/>
+      <c r="D69" s="83">
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A70" s="68"/>
-      <c r="B70" s="68"/>
-      <c r="C70" s="68"/>
+      <c r="A70" s="62"/>
+      <c r="B70" s="62"/>
+      <c r="C70" s="62"/>
     </row>
     <row r="71" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A71" s="124" t="s">
+      <c r="A71" s="118" t="s">
         <v>36</v>
       </c>
-      <c r="B71" s="125"/>
-      <c r="C71" s="70"/>
-      <c r="D71" s="34">
+      <c r="B71" s="119"/>
+      <c r="C71" s="64"/>
+      <c r="D71" s="28">
         <f>D66+D69</f>
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A72" s="68"/>
-      <c r="B72" s="68"/>
-      <c r="C72" s="68"/>
+      <c r="A72" s="62"/>
+      <c r="B72" s="62"/>
+      <c r="C72" s="62"/>
     </row>
     <row r="73" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A73" s="136" t="s">
+      <c r="A73" s="130" t="s">
         <v>26</v>
       </c>
-      <c r="B73" s="137">
+      <c r="B73" s="131">
         <f>D61</f>
-        <v>1627544.95</v>
-      </c>
-      <c r="C73" s="138"/>
+        <v>1508578.46</v>
+      </c>
+      <c r="C73" s="132"/>
     </row>
     <row r="74" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A74" s="136" t="s">
+      <c r="A74" s="130" t="s">
         <v>27</v>
       </c>
-      <c r="B74" s="137">
+      <c r="B74" s="131">
         <f>D61-D59</f>
-        <v>1509108.42</v>
-      </c>
-      <c r="C74" s="68"/>
+        <v>1508578.46</v>
+      </c>
+      <c r="C74" s="62"/>
     </row>
     <row r="75" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A75" s="136" t="s">
+      <c r="A75" s="130" t="s">
         <v>37</v>
       </c>
-      <c r="B75" s="137">
+      <c r="B75" s="131">
         <f>D71-D69</f>
         <v>0</v>
       </c>
-      <c r="C75" s="68"/>
+      <c r="C75" s="62"/>
     </row>
     <row r="76" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A76" s="136" t="s">
+      <c r="A76" s="130" t="s">
         <v>52</v>
       </c>
-      <c r="B76" s="137">
+      <c r="B76" s="131">
         <f>D71</f>
         <v>0</v>
       </c>
-      <c r="C76" s="68"/>
+      <c r="C76" s="62"/>
     </row>
     <row r="77" spans="1:4">
-      <c r="A77" s="68"/>
-      <c r="B77" s="68"/>
-      <c r="C77" s="68"/>
+      <c r="A77" s="62"/>
+      <c r="B77" s="62"/>
+      <c r="C77" s="62"/>
       <c r="D77" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="78" spans="1:4">
-      <c r="A78" s="68"/>
-      <c r="B78" s="68"/>
-      <c r="C78" s="68"/>
+      <c r="A78" s="62"/>
+      <c r="B78" s="62"/>
+      <c r="C78" s="62"/>
     </row>
     <row r="79" spans="1:4">
-      <c r="A79" s="68"/>
-      <c r="B79" s="68"/>
-      <c r="C79" s="68"/>
+      <c r="A79" s="62"/>
+      <c r="B79" s="62"/>
+      <c r="C79" s="62"/>
     </row>
     <row r="80" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A80" s="139" t="s">
+      <c r="A80" s="133" t="s">
         <v>47</v>
       </c>
-      <c r="B80" s="140"/>
-      <c r="C80" s="68"/>
+      <c r="B80" s="134"/>
+      <c r="C80" s="62"/>
     </row>
     <row r="81" spans="1:12" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A81" s="12" t="s">
+      <c r="A81" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B81" s="141">
-        <v>1223485.8199999998</v>
-      </c>
-      <c r="C81" s="68"/>
+      <c r="B81" s="135">
+        <v>1118920.2499999998</v>
+      </c>
+      <c r="C81" s="62"/>
     </row>
     <row r="82" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A82" s="142" t="s">
+      <c r="A82" s="136" t="s">
         <v>55</v>
       </c>
-      <c r="B82" s="62">
+      <c r="B82" s="56">
         <f>PRORRATEO!H24</f>
-        <v>1194404.8999999994</v>
-      </c>
-      <c r="C82" s="68"/>
+        <v>1393375.9</v>
+      </c>
+      <c r="C82" s="62"/>
     </row>
     <row r="83" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A83" s="142" t="s">
+      <c r="A83" s="136" t="s">
         <v>54</v>
       </c>
-      <c r="B83" s="62">
+      <c r="B83" s="56">
         <f>B92</f>
         <v>0</v>
       </c>
-      <c r="C83" s="68"/>
+      <c r="C83" s="62"/>
+      <c r="F83" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="84" spans="1:12">
-      <c r="A84" s="144" t="s">
+      <c r="A84" s="138" t="s">
         <v>38</v>
       </c>
-      <c r="B84" s="150">
+      <c r="B84" s="144">
         <f>-B74</f>
-        <v>-1509108.42</v>
-      </c>
-      <c r="C84" s="68"/>
+        <v>-1508578.46</v>
+      </c>
+      <c r="C84" s="62"/>
     </row>
     <row r="85" spans="1:12">
-      <c r="A85" s="143" t="s">
+      <c r="A85" s="137" t="s">
         <v>39</v>
       </c>
-      <c r="B85" s="62">
+      <c r="B85" s="56">
         <f>-(B75)</f>
         <v>0</v>
       </c>
-      <c r="C85" s="68"/>
+      <c r="C85" s="62"/>
     </row>
     <row r="86" spans="1:12">
-      <c r="A86" s="11" t="s">
+      <c r="A86" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B86" s="104">
+      <c r="B86" s="98">
         <f>SUM(B81:B85)</f>
-        <v>908782.29999999935</v>
-      </c>
-      <c r="C86" s="129"/>
+        <v>1003717.6899999995</v>
+      </c>
+      <c r="C86" s="123"/>
     </row>
     <row r="87" spans="1:12" ht="34.5" customHeight="1">
-      <c r="B87" s="22"/>
-      <c r="C87" s="24"/>
-      <c r="D87" s="129"/>
+      <c r="B87" s="16"/>
+      <c r="C87" s="18"/>
+      <c r="D87" s="123"/>
     </row>
     <row r="88" spans="1:12">
-      <c r="A88" s="161" t="s">
+      <c r="A88" s="151" t="s">
         <v>46</v>
       </c>
-      <c r="B88" s="161"/>
+      <c r="B88" s="151"/>
     </row>
     <row r="89" spans="1:12" ht="27.75" customHeight="1">
-      <c r="A89" s="161"/>
-      <c r="B89" s="161"/>
+      <c r="A89" s="151"/>
+      <c r="B89" s="151"/>
     </row>
     <row r="90" spans="1:12" ht="32.25" customHeight="1">
-      <c r="A90" s="74"/>
-      <c r="B90" s="18"/>
+      <c r="A90" s="68"/>
+      <c r="B90" s="12"/>
     </row>
     <row r="91" spans="1:12" ht="32.25" customHeight="1">
-      <c r="A91" s="74"/>
-      <c r="B91" s="18"/>
+      <c r="A91" s="68"/>
+      <c r="B91" s="12"/>
     </row>
     <row r="92" spans="1:12">
-      <c r="A92" s="25" t="s">
+      <c r="A92" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B92" s="75">
+      <c r="B92" s="69">
         <f>SUM(B90:B91)</f>
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:12">
-      <c r="L93" s="4"/>
+      <c r="L93" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -3036,1440 +3036,1451 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="12.95" customHeight="1">
-      <c r="A1" s="105"/>
-      <c r="B1" s="170" t="str">
+      <c r="A1" s="99"/>
+      <c r="B1" s="160" t="str">
         <f>RESUMEN!A4</f>
         <v xml:space="preserve">Titular: CONSORCIO DE PROPIETARIOS CORONEL BELTRAN 34
 Banco Santander: Cta Corriente en Pesos 533-030591/4
 Cuit del consorcio: 30-71897608-8
 CBU: 0720533020000003059140 - Alias: SALMON.ARMADA.FOCO                                                                                                                                                                                                                                                                                                      </v>
       </c>
-      <c r="C1" s="170"/>
-      <c r="D1" s="170"/>
-      <c r="E1" s="170"/>
-      <c r="F1" s="170"/>
-      <c r="G1" s="170"/>
-      <c r="H1" s="170"/>
-      <c r="I1" s="170"/>
-      <c r="J1" s="170"/>
-      <c r="K1" s="170"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="107"/>
+      <c r="C1" s="160"/>
+      <c r="D1" s="160"/>
+      <c r="E1" s="160"/>
+      <c r="F1" s="160"/>
+      <c r="G1" s="160"/>
+      <c r="H1" s="160"/>
+      <c r="I1" s="160"/>
+      <c r="J1" s="160"/>
+      <c r="K1" s="160"/>
+      <c r="L1" s="100"/>
+      <c r="M1" s="100"/>
+      <c r="N1" s="100"/>
+      <c r="O1" s="100"/>
+      <c r="P1" s="101"/>
     </row>
     <row r="2" spans="1:21" ht="33.75" customHeight="1">
-      <c r="A2" s="108"/>
-      <c r="B2" s="171"/>
-      <c r="C2" s="171"/>
-      <c r="D2" s="171"/>
-      <c r="E2" s="171"/>
-      <c r="F2" s="171"/>
-      <c r="G2" s="171"/>
-      <c r="H2" s="171"/>
-      <c r="I2" s="171"/>
-      <c r="J2" s="171"/>
-      <c r="K2" s="171"/>
-      <c r="L2" s="109"/>
-      <c r="M2" s="109" t="s">
+      <c r="A2" s="102"/>
+      <c r="B2" s="161"/>
+      <c r="C2" s="161"/>
+      <c r="D2" s="161"/>
+      <c r="E2" s="161"/>
+      <c r="F2" s="161"/>
+      <c r="G2" s="161"/>
+      <c r="H2" s="161"/>
+      <c r="I2" s="161"/>
+      <c r="J2" s="161"/>
+      <c r="K2" s="161"/>
+      <c r="L2" s="103"/>
+      <c r="M2" s="103" t="s">
         <v>4</v>
       </c>
-      <c r="N2" s="3"/>
-      <c r="O2" s="116">
-        <v>1646848.23</v>
-      </c>
-      <c r="P2" s="110"/>
-      <c r="Q2" s="9"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="110">
+        <v>1508578.46</v>
+      </c>
+      <c r="P2" s="104"/>
+      <c r="Q2" s="4"/>
       <c r="R2">
         <v>1646848.23</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="46.5" customHeight="1" thickBot="1">
-      <c r="A3" s="111"/>
-      <c r="B3" s="172"/>
-      <c r="C3" s="172"/>
-      <c r="D3" s="172"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="172"/>
-      <c r="H3" s="172"/>
-      <c r="I3" s="172"/>
-      <c r="J3" s="172"/>
-      <c r="K3" s="172"/>
-      <c r="L3" s="112"/>
-      <c r="M3" s="112" t="s">
+      <c r="A3" s="105"/>
+      <c r="B3" s="162"/>
+      <c r="C3" s="162"/>
+      <c r="D3" s="162"/>
+      <c r="E3" s="162"/>
+      <c r="F3" s="162"/>
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="162"/>
+      <c r="K3" s="162"/>
+      <c r="L3" s="106"/>
+      <c r="M3" s="106" t="s">
         <v>56</v>
       </c>
-      <c r="N3" s="113"/>
-      <c r="O3" s="146">
-        <v>0</v>
-      </c>
-      <c r="P3" s="114"/>
+      <c r="N3" s="107"/>
+      <c r="O3" s="140">
+        <v>0</v>
+      </c>
+      <c r="P3" s="108"/>
     </row>
     <row r="4" spans="1:21" ht="30.6" customHeight="1" thickBot="1">
-      <c r="A4" s="3"/>
-      <c r="B4" s="182" t="s">
+      <c r="A4" s="2"/>
+      <c r="B4" s="173" t="s">
         <v>97</v>
       </c>
-      <c r="C4" s="183"/>
-      <c r="D4" s="183"/>
-      <c r="E4" s="183"/>
-      <c r="F4" s="183"/>
-      <c r="G4" s="183"/>
-      <c r="H4" s="183"/>
-      <c r="I4" s="183"/>
-      <c r="J4" s="183"/>
-      <c r="K4" s="183"/>
-      <c r="L4" s="183"/>
-      <c r="M4" s="183"/>
-      <c r="N4" s="183"/>
-      <c r="O4" s="183"/>
-      <c r="P4" s="184"/>
+      <c r="C4" s="174"/>
+      <c r="D4" s="174"/>
+      <c r="E4" s="174"/>
+      <c r="F4" s="174"/>
+      <c r="G4" s="174"/>
+      <c r="H4" s="174"/>
+      <c r="I4" s="174"/>
+      <c r="J4" s="174"/>
+      <c r="K4" s="174"/>
+      <c r="L4" s="174"/>
+      <c r="M4" s="174"/>
+      <c r="N4" s="174"/>
+      <c r="O4" s="174"/>
+      <c r="P4" s="175"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="166" t="s">
+      <c r="A5" s="176" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="168" t="s">
+      <c r="B5" s="178" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="169" t="s">
+      <c r="C5" s="165" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="169" t="s">
+      <c r="D5" s="165" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="169" t="s">
+      <c r="E5" s="165" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="169" t="s">
+      <c r="F5" s="165" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="169" t="s">
+      <c r="G5" s="165" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="169" t="s">
+      <c r="H5" s="165" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="169" t="s">
+      <c r="I5" s="165" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="178" t="s">
+      <c r="J5" s="169" t="s">
         <v>44</v>
       </c>
-      <c r="K5" s="176" t="s">
+      <c r="K5" s="167" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="176" t="s">
+      <c r="L5" s="167" t="s">
         <v>10</v>
       </c>
-      <c r="M5" s="176" t="s">
+      <c r="M5" s="167" t="s">
         <v>40</v>
       </c>
-      <c r="N5" s="180" t="s">
+      <c r="N5" s="171" t="s">
         <v>51</v>
       </c>
-      <c r="O5" s="94" t="s">
+      <c r="O5" s="88" t="s">
         <v>50</v>
       </c>
-      <c r="P5" s="173" t="s">
+      <c r="P5" s="163" t="s">
         <v>49</v>
       </c>
-      <c r="S5" s="24"/>
-      <c r="T5" s="22"/>
+      <c r="S5" s="18"/>
+      <c r="T5" s="16"/>
     </row>
     <row r="6" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A6" s="167"/>
-      <c r="B6" s="168"/>
-      <c r="C6" s="169"/>
-      <c r="D6" s="169"/>
-      <c r="E6" s="175"/>
-      <c r="F6" s="169"/>
-      <c r="G6" s="169"/>
-      <c r="H6" s="169"/>
-      <c r="I6" s="175"/>
-      <c r="J6" s="179"/>
-      <c r="K6" s="177"/>
-      <c r="L6" s="176"/>
-      <c r="M6" s="177"/>
-      <c r="N6" s="181"/>
-      <c r="O6" s="29" t="str">
+      <c r="A6" s="177"/>
+      <c r="B6" s="178"/>
+      <c r="C6" s="165"/>
+      <c r="D6" s="165"/>
+      <c r="E6" s="166"/>
+      <c r="F6" s="165"/>
+      <c r="G6" s="165"/>
+      <c r="H6" s="165"/>
+      <c r="I6" s="166"/>
+      <c r="J6" s="170"/>
+      <c r="K6" s="168"/>
+      <c r="L6" s="167"/>
+      <c r="M6" s="168"/>
+      <c r="N6" s="172"/>
+      <c r="O6" s="23" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 17/09</v>
       </c>
-      <c r="P6" s="173"/>
-      <c r="S6" s="22">
+      <c r="P6" s="163"/>
+      <c r="S6" s="16">
         <v>65160</v>
       </c>
-      <c r="T6" s="22">
+      <c r="T6" s="16">
         <v>157470</v>
       </c>
-      <c r="U6" s="24">
+      <c r="U6" s="18">
         <f>T6+S6</f>
         <v>222630</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="17.100000000000001" customHeight="1">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="31">
+      <c r="B7" s="25">
         <v>1</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="C7" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="D7" s="31" t="s">
+      <c r="D7" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="E7" s="31"/>
-      <c r="F7" s="35">
+      <c r="E7" s="25"/>
+      <c r="F7" s="29">
         <v>10.86</v>
       </c>
-      <c r="G7" s="36">
+      <c r="G7" s="30">
         <v>5442105.0099999998</v>
       </c>
-      <c r="H7" s="151"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="39">
+      <c r="H7" s="31"/>
+      <c r="I7" s="32"/>
+      <c r="J7" s="33">
         <f>G7-H7</f>
         <v>5442105.0099999998</v>
       </c>
-      <c r="K7" s="39">
+      <c r="K7" s="33">
         <f>IF(J7&gt;0,J7*3%,0)</f>
         <v>163263.15029999998</v>
       </c>
-      <c r="L7" s="40">
+      <c r="L7" s="34">
         <f>O$3*F7%</f>
         <v>0</v>
       </c>
-      <c r="M7" s="40">
+      <c r="M7" s="34">
         <f>O$2*F7%</f>
-        <v>178847.71777799999</v>
-      </c>
-      <c r="N7" s="41">
+        <v>163831.62075599999</v>
+      </c>
+      <c r="N7" s="35">
         <v>75000</v>
       </c>
-      <c r="O7" s="42">
+      <c r="O7" s="36">
         <f>ROUND(SUM(J7:N7),0) + Q7</f>
-        <v>5859216.0099999998</v>
-      </c>
-      <c r="P7" s="43">
+        <v>5844200.0099999998</v>
+      </c>
+      <c r="P7" s="37">
         <f t="shared" ref="P7:P23" si="0">ROUND(O7*3%,0) + O7</f>
-        <v>6034992.0099999998</v>
-      </c>
-      <c r="Q7" s="24">
+        <v>6019526.0099999998</v>
+      </c>
+      <c r="Q7" s="18">
         <v>0.01</v>
       </c>
-      <c r="S7" s="22">
+      <c r="S7" s="16">
         <v>66960</v>
       </c>
-      <c r="T7" s="22">
+      <c r="T7" s="16">
         <v>161820</v>
       </c>
-      <c r="U7" s="24">
+      <c r="U7" s="18">
         <f t="shared" ref="U7:U21" si="1">T7+S7</f>
         <v>228780</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="17.100000000000001" customHeight="1">
-      <c r="A8" s="152" t="s">
+      <c r="A8" s="145" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="84">
+      <c r="B8" s="78">
         <v>2</v>
       </c>
-      <c r="C8" s="84" t="s">
+      <c r="C8" s="78" t="s">
         <v>67</v>
       </c>
-      <c r="D8" s="84" t="s">
+      <c r="D8" s="78" t="s">
         <v>83</v>
       </c>
-      <c r="E8" s="96"/>
-      <c r="F8" s="35">
+      <c r="E8" s="90"/>
+      <c r="F8" s="29">
         <v>11.16</v>
       </c>
-      <c r="G8" s="36">
-        <v>183788.02</v>
-      </c>
-      <c r="H8" s="37"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="39">
+      <c r="G8" s="30">
+        <v>189302.02</v>
+      </c>
+      <c r="H8" s="31">
+        <f>198971-H18</f>
+        <v>189301.88</v>
+      </c>
+      <c r="I8" s="32"/>
+      <c r="J8" s="33">
         <f t="shared" ref="J8:J22" si="2">G8-H8</f>
-        <v>183788.02</v>
-      </c>
-      <c r="K8" s="39">
+        <v>0.13999999998486601</v>
+      </c>
+      <c r="K8" s="33">
         <f t="shared" ref="K8:K22" si="3">IF(J8&gt;0,J8*3%,0)</f>
-        <v>5513.6405999999997</v>
-      </c>
-      <c r="L8" s="40">
+        <v>4.1999999995459801E-3</v>
+      </c>
+      <c r="L8" s="34">
         <f t="shared" ref="L8:L23" si="4">O$3*F8%</f>
         <v>0</v>
       </c>
-      <c r="M8" s="40">
+      <c r="M8" s="34">
         <f t="shared" ref="M8:M23" si="5">O$2*F8%</f>
-        <v>183788.262468</v>
-      </c>
-      <c r="N8" s="41">
-        <v>0</v>
-      </c>
-      <c r="O8" s="42">
+        <v>168357.35613600002</v>
+      </c>
+      <c r="N8" s="35">
+        <v>0</v>
+      </c>
+      <c r="O8" s="36">
         <f>ROUND(SUM(J8:N8),0) + Q8</f>
-        <v>373090.02</v>
-      </c>
-      <c r="P8" s="43">
+        <v>168358.02</v>
+      </c>
+      <c r="P8" s="37">
         <f t="shared" si="0"/>
-        <v>384283.02</v>
-      </c>
-      <c r="Q8" s="24">
+        <v>173409.02</v>
+      </c>
+      <c r="Q8" s="18">
         <f>Q7+0.01</f>
         <v>0.02</v>
       </c>
-      <c r="R8" s="24"/>
-      <c r="S8" s="22">
+      <c r="R8" s="18"/>
+      <c r="S8" s="16">
         <v>41700</v>
       </c>
-      <c r="T8" s="22">
+      <c r="T8" s="16">
         <v>100775</v>
       </c>
-      <c r="U8" s="24">
+      <c r="U8" s="18">
         <f t="shared" si="1"/>
         <v>142475</v>
       </c>
     </row>
     <row r="9" spans="1:21" ht="17.100000000000001" customHeight="1">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="84">
+      <c r="B9" s="78">
         <v>4</v>
       </c>
-      <c r="C9" s="84" t="s">
+      <c r="C9" s="78" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="95" t="s">
+      <c r="D9" s="89" t="s">
         <v>84</v>
       </c>
-      <c r="E9" s="84" t="s">
+      <c r="E9" s="78" t="s">
         <v>106</v>
       </c>
-      <c r="F9" s="97">
+      <c r="F9" s="91">
         <v>6.95</v>
       </c>
-      <c r="G9" s="37">
+      <c r="G9" s="31">
         <v>232394.03</v>
       </c>
-      <c r="H9" s="151">
+      <c r="H9" s="31">
         <v>114505</v>
       </c>
-      <c r="I9" s="38"/>
-      <c r="J9" s="98">
+      <c r="I9" s="32"/>
+      <c r="J9" s="92">
         <f t="shared" si="2"/>
         <v>117889.03</v>
       </c>
-      <c r="K9" s="39">
+      <c r="K9" s="33">
         <f t="shared" si="3"/>
         <v>3536.6708999999996</v>
       </c>
-      <c r="L9" s="99">
+      <c r="L9" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M9" s="99">
+      <c r="M9" s="93">
         <f t="shared" si="5"/>
-        <v>114455.95198500001</v>
-      </c>
-      <c r="N9" s="100">
-        <v>0</v>
-      </c>
-      <c r="O9" s="101">
+        <v>104846.20297000001</v>
+      </c>
+      <c r="N9" s="94">
+        <v>0</v>
+      </c>
+      <c r="O9" s="95">
         <f t="shared" ref="O9:O23" si="6">ROUND(SUM(J9:N9),0) + Q9</f>
-        <v>235882.03</v>
-      </c>
-      <c r="P9" s="102">
+        <v>226272.03</v>
+      </c>
+      <c r="P9" s="96">
         <f t="shared" si="0"/>
-        <v>242958.03</v>
-      </c>
-      <c r="Q9" s="24">
+        <v>233060.03</v>
+      </c>
+      <c r="Q9" s="18">
         <f t="shared" ref="Q9:Q22" si="7">Q8+0.01</f>
         <v>0.03</v>
       </c>
-      <c r="S9" s="22">
+      <c r="S9" s="16">
         <v>44220</v>
       </c>
-      <c r="T9" s="22">
+      <c r="T9" s="16">
         <v>106865</v>
       </c>
-      <c r="U9" s="24">
+      <c r="U9" s="18">
         <f t="shared" si="1"/>
         <v>151085</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="17.100000000000001" customHeight="1">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="84">
+      <c r="B10" s="78">
         <v>3</v>
       </c>
-      <c r="C10" s="84" t="s">
+      <c r="C10" s="78" t="s">
         <v>69</v>
       </c>
-      <c r="D10" s="84" t="s">
+      <c r="D10" s="78" t="s">
         <v>85</v>
       </c>
-      <c r="E10" s="84" t="s">
+      <c r="E10" s="78" t="s">
         <v>112</v>
       </c>
-      <c r="F10" s="35">
+      <c r="F10" s="29">
         <v>7.37</v>
       </c>
-      <c r="G10" s="36">
+      <c r="G10" s="30">
         <v>168311.04000000001</v>
       </c>
-      <c r="H10" s="151">
+      <c r="H10" s="31">
         <f>129937-H20</f>
         <v>121372.86</v>
       </c>
-      <c r="I10" s="38"/>
-      <c r="J10" s="39">
+      <c r="I10" s="32"/>
+      <c r="J10" s="33">
         <f t="shared" si="2"/>
         <v>46938.180000000008</v>
       </c>
-      <c r="K10" s="39">
+      <c r="K10" s="33">
         <f t="shared" si="3"/>
         <v>1408.1454000000001</v>
       </c>
-      <c r="L10" s="40">
+      <c r="L10" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M10" s="40">
+      <c r="M10" s="34">
         <f t="shared" si="5"/>
-        <v>121372.714551</v>
-      </c>
-      <c r="N10" s="41">
-        <v>0</v>
-      </c>
-      <c r="O10" s="42">
+        <v>111182.232502</v>
+      </c>
+      <c r="N10" s="35">
+        <v>0</v>
+      </c>
+      <c r="O10" s="36">
         <f t="shared" si="6"/>
-        <v>169719.04000000001</v>
-      </c>
-      <c r="P10" s="43">
+        <v>159529.04</v>
+      </c>
+      <c r="P10" s="37">
         <f t="shared" si="0"/>
-        <v>174811.04</v>
-      </c>
-      <c r="Q10" s="24">
+        <v>164315.04</v>
+      </c>
+      <c r="Q10" s="18">
         <f t="shared" si="7"/>
         <v>0.04</v>
       </c>
-      <c r="S10" s="22">
+      <c r="S10" s="16">
         <v>64080</v>
       </c>
-      <c r="T10" s="22">
+      <c r="T10" s="16">
         <v>154860</v>
       </c>
-      <c r="U10" s="24">
+      <c r="U10" s="18">
         <f t="shared" si="1"/>
         <v>218940</v>
       </c>
     </row>
     <row r="11" spans="1:21" ht="27" customHeight="1">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="31">
+      <c r="B11" s="25">
         <v>5</v>
       </c>
-      <c r="C11" s="31" t="s">
+      <c r="C11" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="31" t="s">
+      <c r="D11" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="E11" s="32" t="s">
+      <c r="E11" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="F11" s="35">
+      <c r="F11" s="29">
         <v>10.68</v>
       </c>
-      <c r="G11" s="36">
+      <c r="G11" s="30">
         <v>170607.05</v>
       </c>
-      <c r="H11" s="151">
+      <c r="H11" s="31">
         <f>G11</f>
         <v>170607.05</v>
       </c>
-      <c r="I11" s="38"/>
-      <c r="J11" s="39">
+      <c r="I11" s="32"/>
+      <c r="J11" s="33">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K11" s="39">
+      <c r="K11" s="33">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L11" s="40">
+      <c r="L11" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M11" s="40">
+      <c r="M11" s="34">
         <f t="shared" si="5"/>
-        <v>175883.39096399999</v>
-      </c>
-      <c r="N11" s="41">
-        <v>0</v>
-      </c>
-      <c r="O11" s="42">
+        <v>161116.17952799998</v>
+      </c>
+      <c r="N11" s="35">
+        <v>0</v>
+      </c>
+      <c r="O11" s="36">
         <f t="shared" si="6"/>
-        <v>175883.05</v>
-      </c>
-      <c r="P11" s="43">
+        <v>161116.04999999999</v>
+      </c>
+      <c r="P11" s="37">
         <f t="shared" si="0"/>
-        <v>181159.05</v>
-      </c>
-      <c r="Q11" s="24">
+        <v>165949.04999999999</v>
+      </c>
+      <c r="Q11" s="18">
         <f t="shared" si="7"/>
         <v>0.05</v>
       </c>
-      <c r="S11" s="22">
+      <c r="S11" s="16">
         <v>41700</v>
       </c>
-      <c r="T11" s="22">
+      <c r="T11" s="16">
         <v>100775</v>
       </c>
-      <c r="U11" s="24">
+      <c r="U11" s="18">
         <f t="shared" si="1"/>
         <v>142475</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="17.100000000000001" customHeight="1">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="31">
+      <c r="B12" s="25">
         <v>7</v>
       </c>
-      <c r="C12" s="31" t="s">
+      <c r="C12" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="D12" s="31" t="s">
+      <c r="D12" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="E12" s="31" t="s">
+      <c r="E12" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="F12" s="35">
+      <c r="F12" s="29">
         <v>6.95</v>
       </c>
-      <c r="G12" s="36">
+      <c r="G12" s="30">
         <v>114456.06</v>
       </c>
-      <c r="H12" s="151">
+      <c r="H12" s="31">
         <f>G12</f>
         <v>114456.06</v>
       </c>
-      <c r="I12" s="38"/>
-      <c r="J12" s="39">
+      <c r="I12" s="32"/>
+      <c r="J12" s="33">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K12" s="39">
+      <c r="K12" s="33">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L12" s="40">
+      <c r="L12" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M12" s="40">
+      <c r="M12" s="34">
         <f t="shared" si="5"/>
-        <v>114455.95198500001</v>
-      </c>
-      <c r="N12" s="128">
-        <v>0</v>
-      </c>
-      <c r="O12" s="42">
+        <v>104846.20297000001</v>
+      </c>
+      <c r="N12" s="122">
+        <v>0</v>
+      </c>
+      <c r="O12" s="36">
         <f>ROUND(SUM(J12:N12),0) + Q12</f>
-        <v>114456.06</v>
-      </c>
-      <c r="P12" s="43">
+        <v>104846.06</v>
+      </c>
+      <c r="P12" s="37">
         <f t="shared" si="0"/>
-        <v>117890.06</v>
-      </c>
-      <c r="Q12" s="24">
+        <v>107991.06</v>
+      </c>
+      <c r="Q12" s="18">
         <f t="shared" si="7"/>
         <v>6.0000000000000005E-2</v>
       </c>
-      <c r="S12" s="22">
+      <c r="S12" s="16">
         <v>41340</v>
       </c>
-      <c r="T12" s="22">
+      <c r="T12" s="16">
         <v>99905</v>
       </c>
-      <c r="U12" s="24">
+      <c r="U12" s="18">
         <f t="shared" si="1"/>
         <v>141245</v>
       </c>
     </row>
     <row r="13" spans="1:21" ht="17.100000000000001" customHeight="1">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="31">
+      <c r="B13" s="25">
         <v>6</v>
       </c>
-      <c r="C13" s="84" t="s">
+      <c r="C13" s="78" t="s">
         <v>72</v>
       </c>
-      <c r="D13" s="84" t="s">
+      <c r="D13" s="78" t="s">
         <v>88</v>
       </c>
-      <c r="E13" s="31" t="s">
+      <c r="E13" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="F13" s="35">
+      <c r="F13" s="29">
         <v>6.89</v>
       </c>
-      <c r="G13" s="36">
+      <c r="G13" s="30">
         <v>113468.07</v>
       </c>
-      <c r="H13" s="151">
+      <c r="H13" s="31">
         <f>G13</f>
         <v>113468.07</v>
       </c>
-      <c r="I13" s="38"/>
-      <c r="J13" s="39">
+      <c r="I13" s="32"/>
+      <c r="J13" s="33">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K13" s="39">
+      <c r="K13" s="33">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L13" s="40">
+      <c r="L13" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M13" s="40">
+      <c r="M13" s="34">
         <f t="shared" si="5"/>
-        <v>113467.843047</v>
-      </c>
-      <c r="N13" s="41">
-        <v>0</v>
-      </c>
-      <c r="O13" s="42">
+        <v>103941.055894</v>
+      </c>
+      <c r="N13" s="35">
+        <v>0</v>
+      </c>
+      <c r="O13" s="36">
         <f t="shared" si="6"/>
-        <v>113468.07</v>
-      </c>
-      <c r="P13" s="43">
+        <v>103941.07</v>
+      </c>
+      <c r="P13" s="37">
         <f t="shared" si="0"/>
-        <v>116872.07</v>
-      </c>
-      <c r="Q13" s="24">
+        <v>107059.07</v>
+      </c>
+      <c r="Q13" s="18">
         <f t="shared" si="7"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="R13" s="82"/>
-      <c r="S13" s="115">
+      <c r="R13" s="76"/>
+      <c r="S13" s="109">
         <v>64080</v>
       </c>
-      <c r="T13" s="22">
+      <c r="T13" s="16">
         <v>154860</v>
       </c>
-      <c r="U13" s="24">
+      <c r="U13" s="18">
         <f t="shared" si="1"/>
         <v>218940</v>
       </c>
     </row>
     <row r="14" spans="1:21" ht="17.100000000000001" customHeight="1">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="25">
         <v>8</v>
       </c>
-      <c r="C14" s="31" t="s">
+      <c r="C14" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="D14" s="31" t="s">
+      <c r="D14" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="E14" s="31" t="s">
+      <c r="E14" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="F14" s="35">
+      <c r="F14" s="29">
         <v>10.68</v>
       </c>
-      <c r="G14" s="36">
+      <c r="G14" s="30">
         <v>175883.08</v>
       </c>
-      <c r="H14" s="151">
+      <c r="H14" s="31">
         <f>G14</f>
         <v>175883.08</v>
       </c>
-      <c r="I14" s="38"/>
-      <c r="J14" s="39">
+      <c r="I14" s="32"/>
+      <c r="J14" s="33">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K14" s="39">
+      <c r="K14" s="33">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L14" s="40">
+      <c r="L14" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M14" s="40">
+      <c r="M14" s="34">
         <f t="shared" si="5"/>
-        <v>175883.39096399999</v>
-      </c>
-      <c r="N14" s="41">
-        <v>0</v>
-      </c>
-      <c r="O14" s="42">
+        <v>161116.17952799998</v>
+      </c>
+      <c r="N14" s="35">
+        <v>0</v>
+      </c>
+      <c r="O14" s="36">
         <f t="shared" si="6"/>
-        <v>175883.08</v>
-      </c>
-      <c r="P14" s="43">
+        <v>161116.07999999999</v>
+      </c>
+      <c r="P14" s="37">
         <f t="shared" si="0"/>
-        <v>181159.08</v>
-      </c>
-      <c r="Q14" s="24">
+        <v>165949.07999999999</v>
+      </c>
+      <c r="Q14" s="18">
         <f t="shared" si="7"/>
         <v>0.08</v>
       </c>
-      <c r="S14" s="22">
+      <c r="S14" s="16">
         <v>41700</v>
       </c>
-      <c r="T14" s="22">
+      <c r="T14" s="16">
         <v>100775</v>
       </c>
-      <c r="U14" s="24">
+      <c r="U14" s="18">
         <f t="shared" si="1"/>
         <v>142475</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="17.100000000000001" customHeight="1">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="84">
+      <c r="B15" s="78">
         <v>10</v>
       </c>
-      <c r="C15" s="84" t="s">
+      <c r="C15" s="78" t="s">
         <v>74</v>
       </c>
-      <c r="D15" s="84" t="s">
+      <c r="D15" s="78" t="s">
         <v>89</v>
       </c>
-      <c r="E15" s="96" t="s">
+      <c r="E15" s="90" t="s">
         <v>109</v>
       </c>
-      <c r="F15" s="97">
+      <c r="F15" s="91">
         <v>6.95</v>
       </c>
-      <c r="G15" s="37">
+      <c r="G15" s="31">
         <v>39268.089999999997</v>
       </c>
-      <c r="H15" s="151">
+      <c r="H15" s="31">
         <f>G15</f>
         <v>39268.089999999997</v>
       </c>
-      <c r="I15" s="38"/>
-      <c r="J15" s="98">
+      <c r="I15" s="32"/>
+      <c r="J15" s="92">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K15" s="98">
-        <v>0</v>
-      </c>
-      <c r="L15" s="99">
+      <c r="K15" s="92">
+        <v>0</v>
+      </c>
+      <c r="L15" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M15" s="99">
+      <c r="M15" s="93">
         <f t="shared" si="5"/>
-        <v>114455.95198500001</v>
-      </c>
-      <c r="N15" s="100">
-        <v>0</v>
-      </c>
-      <c r="O15" s="101">
+        <v>104846.20297000001</v>
+      </c>
+      <c r="N15" s="94">
+        <v>0</v>
+      </c>
+      <c r="O15" s="95">
         <f t="shared" si="6"/>
-        <v>114456.09</v>
-      </c>
-      <c r="P15" s="102">
+        <v>104846.09</v>
+      </c>
+      <c r="P15" s="96">
         <f t="shared" si="0"/>
-        <v>117890.09</v>
-      </c>
-      <c r="Q15" s="24">
+        <v>107991.09</v>
+      </c>
+      <c r="Q15" s="18">
         <f t="shared" si="7"/>
         <v>0.09</v>
       </c>
-      <c r="S15" s="22">
+      <c r="S15" s="16">
         <v>41340</v>
       </c>
-      <c r="T15" s="22">
+      <c r="T15" s="16">
         <v>99905</v>
       </c>
-      <c r="U15" s="24">
+      <c r="U15" s="18">
         <f t="shared" si="1"/>
         <v>141245</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="17.100000000000001" customHeight="1">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="31">
+      <c r="B16" s="25">
         <v>9</v>
       </c>
-      <c r="C16" s="31" t="s">
+      <c r="C16" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="D16" s="31" t="s">
+      <c r="D16" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="E16" s="32" t="s">
+      <c r="E16" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="F16" s="35">
+      <c r="F16" s="29">
         <v>6.89</v>
       </c>
-      <c r="G16" s="36">
+      <c r="G16" s="30">
         <v>154767.1</v>
       </c>
-      <c r="H16" s="151">
+      <c r="H16" s="31">
         <v>113468</v>
       </c>
-      <c r="I16" s="38"/>
-      <c r="J16" s="39">
+      <c r="I16" s="32"/>
+      <c r="J16" s="33">
         <f t="shared" si="2"/>
         <v>41299.100000000006</v>
       </c>
-      <c r="K16" s="39">
+      <c r="K16" s="33">
         <f t="shared" si="3"/>
         <v>1238.9730000000002</v>
       </c>
-      <c r="L16" s="40">
+      <c r="L16" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M16" s="40">
+      <c r="M16" s="34">
         <f t="shared" si="5"/>
-        <v>113467.843047</v>
-      </c>
-      <c r="N16" s="41">
-        <v>0</v>
-      </c>
-      <c r="O16" s="42">
+        <v>103941.055894</v>
+      </c>
+      <c r="N16" s="35">
+        <v>0</v>
+      </c>
+      <c r="O16" s="36">
         <f t="shared" si="6"/>
-        <v>156006.1</v>
-      </c>
-      <c r="P16" s="43">
+        <v>146479.1</v>
+      </c>
+      <c r="P16" s="37">
         <f t="shared" si="0"/>
-        <v>160686.1</v>
-      </c>
-      <c r="Q16" s="24">
+        <v>150873.1</v>
+      </c>
+      <c r="Q16" s="18">
         <f t="shared" si="7"/>
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="R16" t="s">
         <v>113</v>
       </c>
-      <c r="S16" s="22">
+      <c r="S16" s="16">
         <v>71280</v>
       </c>
-      <c r="T16" s="22">
+      <c r="T16" s="16">
         <v>172260</v>
       </c>
-      <c r="U16" s="24">
+      <c r="U16" s="18">
         <f t="shared" si="1"/>
         <v>243540</v>
       </c>
     </row>
     <row r="17" spans="1:21" ht="17.100000000000001" customHeight="1">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="31">
+      <c r="B17" s="25">
         <v>11</v>
       </c>
-      <c r="C17" s="31" t="s">
+      <c r="C17" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="D17" s="31" t="s">
+      <c r="D17" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="E17" s="32"/>
-      <c r="F17" s="35">
+      <c r="E17" s="26"/>
+      <c r="F17" s="29">
         <v>11.88</v>
       </c>
-      <c r="G17" s="36">
+      <c r="G17" s="30">
         <v>195646.11</v>
       </c>
-      <c r="H17" s="151">
+      <c r="H17" s="31">
         <f>G17</f>
         <v>195646.11</v>
       </c>
-      <c r="I17" s="38"/>
-      <c r="J17" s="39">
+      <c r="I17" s="32"/>
+      <c r="J17" s="33">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K17" s="39">
+      <c r="K17" s="33">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L17" s="40">
+      <c r="L17" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M17" s="40">
+      <c r="M17" s="34">
         <f t="shared" si="5"/>
-        <v>195645.569724</v>
-      </c>
-      <c r="N17" s="41">
-        <v>0</v>
-      </c>
-      <c r="O17" s="42">
+        <v>179219.121048</v>
+      </c>
+      <c r="N17" s="35">
+        <v>0</v>
+      </c>
+      <c r="O17" s="36">
         <f t="shared" si="6"/>
-        <v>195646.11</v>
-      </c>
-      <c r="P17" s="43">
+        <v>179219.11</v>
+      </c>
+      <c r="P17" s="37">
         <f t="shared" si="0"/>
-        <v>201515.11</v>
-      </c>
-      <c r="Q17" s="24">
+        <v>184596.11</v>
+      </c>
+      <c r="Q17" s="18">
         <f t="shared" si="7"/>
         <v>0.10999999999999999</v>
       </c>
       <c r="R17" t="s">
         <v>111</v>
       </c>
-      <c r="S17" s="22">
+      <c r="S17" s="16">
         <v>3420</v>
       </c>
-      <c r="T17" s="22">
+      <c r="T17" s="16">
         <v>8265</v>
       </c>
-      <c r="U17" s="24">
+      <c r="U17" s="18">
         <f t="shared" si="1"/>
         <v>11685</v>
       </c>
     </row>
     <row r="18" spans="1:21" ht="17.100000000000001" customHeight="1">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="31" t="s">
+      <c r="B18" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="31" t="s">
+      <c r="C18" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="D18" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="E18" s="32"/>
-      <c r="F18" s="35">
+      <c r="E18" s="26"/>
+      <c r="F18" s="29">
         <v>0.56999999999999995</v>
       </c>
-      <c r="G18" s="36">
-        <v>9387.1200000000008</v>
-      </c>
-      <c r="H18" s="37"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="39">
+      <c r="G18" s="30">
+        <v>9669.1200000000008</v>
+      </c>
+      <c r="H18" s="31">
+        <f>G18</f>
+        <v>9669.1200000000008</v>
+      </c>
+      <c r="I18" s="32"/>
+      <c r="J18" s="33">
         <f t="shared" si="2"/>
-        <v>9387.1200000000008</v>
-      </c>
-      <c r="K18" s="39">
+        <v>0</v>
+      </c>
+      <c r="K18" s="33">
         <f t="shared" si="3"/>
-        <v>281.61360000000002</v>
-      </c>
-      <c r="L18" s="40">
+        <v>0</v>
+      </c>
+      <c r="L18" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M18" s="40">
+      <c r="M18" s="34">
         <f t="shared" si="5"/>
-        <v>9387.0349109999988</v>
-      </c>
-      <c r="N18" s="41">
-        <v>0</v>
-      </c>
-      <c r="O18" s="42">
+        <v>8598.8972219999996</v>
+      </c>
+      <c r="N18" s="35">
+        <v>0</v>
+      </c>
+      <c r="O18" s="36">
         <f t="shared" si="6"/>
-        <v>19056.12</v>
-      </c>
-      <c r="P18" s="43">
+        <v>8599.1200000000008</v>
+      </c>
+      <c r="P18" s="37">
         <f t="shared" si="0"/>
-        <v>19628.12</v>
-      </c>
-      <c r="Q18" s="24">
+        <v>8857.1200000000008</v>
+      </c>
+      <c r="Q18" s="18">
         <f t="shared" si="7"/>
         <v>0.11999999999999998</v>
       </c>
-      <c r="S18" s="22">
+      <c r="S18" s="16">
         <v>3120</v>
       </c>
-      <c r="T18" s="22">
+      <c r="T18" s="16">
         <v>7540</v>
       </c>
-      <c r="U18" s="24">
+      <c r="U18" s="18">
         <f t="shared" si="1"/>
         <v>10660</v>
       </c>
     </row>
     <row r="19" spans="1:21" ht="17.100000000000001" customHeight="1">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="31" t="s">
+      <c r="B19" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="C19" s="31" t="s">
+      <c r="C19" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="D19" s="31" t="s">
+      <c r="D19" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="E19" s="32"/>
-      <c r="F19" s="35">
+      <c r="E19" s="26"/>
+      <c r="F19" s="29">
         <v>0.52</v>
       </c>
-      <c r="G19" s="36">
+      <c r="G19" s="30">
         <v>8307.1299999999992</v>
       </c>
-      <c r="H19" s="151">
+      <c r="H19" s="31">
         <v>8556.1299999999992</v>
       </c>
-      <c r="I19" s="38"/>
-      <c r="J19" s="39">
+      <c r="I19" s="32"/>
+      <c r="J19" s="33">
         <f t="shared" si="2"/>
         <v>-249</v>
       </c>
-      <c r="K19" s="39">
+      <c r="K19" s="33">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L19" s="40">
+      <c r="L19" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M19" s="40">
+      <c r="M19" s="34">
         <f t="shared" si="5"/>
-        <v>8563.610795999999</v>
-      </c>
-      <c r="N19" s="41">
-        <v>0</v>
-      </c>
-      <c r="O19" s="42">
+        <v>7844.6079919999993</v>
+      </c>
+      <c r="N19" s="35">
+        <v>0</v>
+      </c>
+      <c r="O19" s="36">
         <f t="shared" si="6"/>
-        <v>8315.1299999999992</v>
-      </c>
-      <c r="P19" s="43">
+        <v>7596.13</v>
+      </c>
+      <c r="P19" s="37">
         <f t="shared" si="0"/>
-        <v>8564.1299999999992</v>
-      </c>
-      <c r="Q19" s="24">
+        <v>7824.13</v>
+      </c>
+      <c r="Q19" s="18">
         <f t="shared" si="7"/>
         <v>0.12999999999999998</v>
       </c>
-      <c r="S19" s="22">
+      <c r="S19" s="16">
         <v>3120</v>
       </c>
-      <c r="T19" s="22">
+      <c r="T19" s="16">
         <v>7540</v>
       </c>
-      <c r="U19" s="24">
+      <c r="U19" s="18">
         <f t="shared" si="1"/>
         <v>10660</v>
       </c>
     </row>
     <row r="20" spans="1:21" ht="17.100000000000001" customHeight="1">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="31" t="s">
+      <c r="B20" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="C20" s="31" t="s">
+      <c r="C20" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="D20" s="31" t="s">
+      <c r="D20" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="E20" s="31" t="s">
+      <c r="E20" s="25" t="s">
         <v>105</v>
       </c>
-      <c r="F20" s="35">
+      <c r="F20" s="29">
         <v>0.52</v>
       </c>
-      <c r="G20" s="36">
+      <c r="G20" s="30">
         <v>8564.14</v>
       </c>
-      <c r="H20" s="151">
+      <c r="H20" s="31">
         <f>G20</f>
         <v>8564.14</v>
       </c>
-      <c r="I20" s="38"/>
-      <c r="J20" s="39">
+      <c r="I20" s="32"/>
+      <c r="J20" s="33">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K20" s="39">
+      <c r="K20" s="33">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L20" s="40">
+      <c r="L20" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M20" s="40">
+      <c r="M20" s="34">
         <f t="shared" si="5"/>
-        <v>8563.610795999999</v>
-      </c>
-      <c r="N20" s="41">
-        <v>0</v>
-      </c>
-      <c r="O20" s="42">
+        <v>7844.6079919999993</v>
+      </c>
+      <c r="N20" s="35">
+        <v>0</v>
+      </c>
+      <c r="O20" s="36">
         <f t="shared" si="6"/>
-        <v>8564.14</v>
-      </c>
-      <c r="P20" s="43">
+        <v>7845.14</v>
+      </c>
+      <c r="P20" s="37">
         <f t="shared" si="0"/>
-        <v>8821.14</v>
-      </c>
-      <c r="Q20" s="24">
+        <v>8080.14</v>
+      </c>
+      <c r="Q20" s="18">
         <f t="shared" si="7"/>
         <v>0.13999999999999999</v>
       </c>
-      <c r="S20" s="22">
+      <c r="S20" s="16">
         <v>3120</v>
       </c>
-      <c r="T20" s="22">
+      <c r="T20" s="16">
         <v>7540</v>
       </c>
-      <c r="U20" s="24">
+      <c r="U20" s="18">
         <f t="shared" si="1"/>
         <v>10660</v>
       </c>
     </row>
     <row r="21" spans="1:21" ht="17.100000000000001" customHeight="1">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="31" t="s">
+      <c r="B21" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="C21" s="31" t="s">
+      <c r="C21" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="D21" s="31" t="s">
+      <c r="D21" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="E21" s="32"/>
-      <c r="F21" s="35">
+      <c r="E21" s="26"/>
+      <c r="F21" s="29">
         <v>0.52</v>
       </c>
-      <c r="G21" s="36">
+      <c r="G21" s="30">
         <v>8564.15</v>
       </c>
-      <c r="H21" s="151">
+      <c r="H21" s="31">
         <f>G21</f>
         <v>8564.15</v>
       </c>
-      <c r="I21" s="38"/>
-      <c r="J21" s="39">
+      <c r="I21" s="32"/>
+      <c r="J21" s="33">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K21" s="39">
+      <c r="K21" s="33">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L21" s="40">
+      <c r="L21" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M21" s="40">
+      <c r="M21" s="34">
         <f t="shared" si="5"/>
-        <v>8563.610795999999</v>
-      </c>
-      <c r="N21" s="41">
-        <v>0</v>
-      </c>
-      <c r="O21" s="42">
+        <v>7844.6079919999993</v>
+      </c>
+      <c r="N21" s="35">
+        <v>0</v>
+      </c>
+      <c r="O21" s="36">
         <f t="shared" si="6"/>
-        <v>8564.15</v>
-      </c>
-      <c r="P21" s="43">
+        <v>7845.15</v>
+      </c>
+      <c r="P21" s="37">
         <f t="shared" si="0"/>
-        <v>8821.15</v>
-      </c>
-      <c r="Q21" s="24">
+        <v>8080.15</v>
+      </c>
+      <c r="Q21" s="18">
         <f t="shared" si="7"/>
         <v>0.15</v>
       </c>
-      <c r="S21" s="22">
+      <c r="S21" s="16">
         <v>3660</v>
       </c>
-      <c r="T21" s="22">
+      <c r="T21" s="16">
         <v>8845</v>
       </c>
-      <c r="U21" s="24">
+      <c r="U21" s="18">
         <f t="shared" si="1"/>
         <v>12505</v>
       </c>
     </row>
     <row r="22" spans="1:21" ht="17.100000000000001" customHeight="1" thickBot="1">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="31" t="s">
+      <c r="B22" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="31" t="s">
+      <c r="C22" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="D22" s="31" t="s">
+      <c r="D22" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="E22" s="31"/>
-      <c r="F22" s="35">
+      <c r="E22" s="25"/>
+      <c r="F22" s="29">
         <v>0.61</v>
       </c>
-      <c r="G22" s="36">
+      <c r="G22" s="30">
         <v>10046.16</v>
       </c>
-      <c r="H22" s="151">
+      <c r="H22" s="31">
         <f>G22</f>
         <v>10046.16</v>
       </c>
-      <c r="I22" s="38"/>
-      <c r="J22" s="39">
+      <c r="I22" s="32"/>
+      <c r="J22" s="33">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K22" s="39">
+      <c r="K22" s="33">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L22" s="40">
+      <c r="L22" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M22" s="40">
+      <c r="M22" s="34">
         <f t="shared" si="5"/>
-        <v>10045.774202999999</v>
-      </c>
-      <c r="N22" s="41">
-        <v>0</v>
-      </c>
-      <c r="O22" s="42">
+        <v>9202.3286059999991</v>
+      </c>
+      <c r="N22" s="35">
+        <v>0</v>
+      </c>
+      <c r="O22" s="36">
         <f t="shared" si="6"/>
-        <v>10046.16</v>
-      </c>
-      <c r="P22" s="43">
+        <v>9202.16</v>
+      </c>
+      <c r="P22" s="37">
         <f t="shared" si="0"/>
-        <v>10347.16</v>
-      </c>
-      <c r="Q22" s="24">
+        <v>9478.16</v>
+      </c>
+      <c r="Q22" s="18">
         <f t="shared" si="7"/>
         <v>0.16</v>
       </c>
-      <c r="S22" s="23"/>
+      <c r="S22" s="17"/>
     </row>
     <row r="23" spans="1:21" ht="15.75" hidden="1" customHeight="1" thickBot="1">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="31"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="44" t="s">
+      <c r="B23" s="25"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="H23" s="37" t="str">
+      <c r="H23" s="31" t="str">
         <f t="shared" ref="H23" si="8">G23</f>
         <v>162450.31</v>
       </c>
-      <c r="I23" s="45"/>
-      <c r="J23" s="46" t="e">
+      <c r="I23" s="39"/>
+      <c r="J23" s="40" t="e">
         <f t="shared" ref="J23" si="9">G23-H23</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K23" s="39" t="e">
+      <c r="K23" s="33" t="e">
         <f t="shared" ref="K23" si="10">IF(J23&gt;0,J23*3%,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L23" s="40">
+      <c r="L23" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M23" s="47">
+      <c r="M23" s="41">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N23" s="48">
-        <v>0</v>
-      </c>
-      <c r="O23" s="42" t="e">
+      <c r="N23" s="42">
+        <v>0</v>
+      </c>
+      <c r="O23" s="36" t="e">
         <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
-      <c r="P23" s="43" t="e">
+      <c r="P23" s="37" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="Q23" s="24"/>
+      <c r="Q23" s="18"/>
     </row>
     <row r="24" spans="1:21" ht="17.100000000000001" customHeight="1" thickBot="1">
-      <c r="B24" s="49"/>
-      <c r="C24" s="50"/>
-      <c r="D24" s="51"/>
-      <c r="E24" s="51"/>
-      <c r="F24" s="52">
+      <c r="B24" s="43"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="46">
         <f>SUM(F7:F23)</f>
         <v>99.999999999999972</v>
       </c>
-      <c r="G24" s="27">
+      <c r="G24" s="21">
         <f>SUM(G7:G23)</f>
-        <v>7035562.3599999994</v>
-      </c>
-      <c r="H24" s="30">
+        <v>7041358.3599999994</v>
+      </c>
+      <c r="H24" s="24">
         <f>SUM(H7:H23)</f>
-        <v>1194404.8999999994</v>
-      </c>
-      <c r="I24" s="30">
+        <v>1393375.9</v>
+      </c>
+      <c r="I24" s="24">
         <f>SUM(I7:I23)</f>
         <v>0</v>
       </c>
-      <c r="J24" s="30"/>
-      <c r="K24" s="30"/>
-      <c r="L24" s="30">
+      <c r="J24" s="24"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="24">
         <f>SUM(L7:L23)</f>
         <v>0</v>
       </c>
-      <c r="M24" s="30">
+      <c r="M24" s="24">
         <f>SUM(M7:M23)</f>
-        <v>1646848.2300000002</v>
-      </c>
-      <c r="N24" s="30">
+        <v>1508578.4599999995</v>
+      </c>
+      <c r="N24" s="24">
         <f>SUM(N7:N23)</f>
         <v>75000</v>
       </c>
-      <c r="O24" s="53">
+      <c r="O24" s="47">
         <f>SUM(O7:O22)</f>
-        <v>7738251.3599999994</v>
-      </c>
-      <c r="P24" s="53">
+        <v>7401010.3599999994</v>
+      </c>
+      <c r="P24" s="47">
         <f>SUM(P7:P22)</f>
-        <v>7970397.3599999994</v>
+        <v>7623038.3599999994</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="12.75" customHeight="1">
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="S25" s="24"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="S25" s="18"/>
     </row>
     <row r="26" spans="1:21" ht="15" hidden="1" customHeight="1"/>
     <row r="27" spans="1:21" ht="15" customHeight="1">
-      <c r="D27" s="174" t="s">
+      <c r="D27" s="164" t="s">
         <v>63</v>
       </c>
-      <c r="E27" s="174"/>
-      <c r="F27" s="174"/>
-      <c r="G27" s="174"/>
-      <c r="H27" s="174"/>
-      <c r="I27" s="174"/>
-      <c r="J27" s="174"/>
-      <c r="K27" s="174"/>
-      <c r="L27" s="174"/>
-      <c r="M27" s="174"/>
-      <c r="N27" s="174"/>
-      <c r="O27" s="174"/>
-      <c r="S27" s="22"/>
+      <c r="E27" s="164"/>
+      <c r="F27" s="164"/>
+      <c r="G27" s="164"/>
+      <c r="H27" s="164"/>
+      <c r="I27" s="164"/>
+      <c r="J27" s="164"/>
+      <c r="K27" s="164"/>
+      <c r="L27" s="164"/>
+      <c r="M27" s="164"/>
+      <c r="N27" s="164"/>
+      <c r="O27" s="164"/>
+      <c r="S27" s="16"/>
     </row>
     <row r="28" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D28" s="174"/>
-      <c r="E28" s="174"/>
-      <c r="F28" s="174"/>
-      <c r="G28" s="174"/>
-      <c r="H28" s="174"/>
-      <c r="I28" s="174"/>
-      <c r="J28" s="174"/>
-      <c r="K28" s="174"/>
-      <c r="L28" s="174"/>
-      <c r="M28" s="174"/>
-      <c r="N28" s="174"/>
-      <c r="O28" s="174"/>
+      <c r="D28" s="164"/>
+      <c r="E28" s="164"/>
+      <c r="F28" s="164"/>
+      <c r="G28" s="164"/>
+      <c r="H28" s="164"/>
+      <c r="I28" s="164"/>
+      <c r="J28" s="164"/>
+      <c r="K28" s="164"/>
+      <c r="L28" s="164"/>
+      <c r="M28" s="164"/>
+      <c r="N28" s="164"/>
+      <c r="O28" s="164"/>
     </row>
     <row r="29" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D29" s="174"/>
-      <c r="E29" s="174"/>
-      <c r="F29" s="174"/>
-      <c r="G29" s="174"/>
-      <c r="H29" s="174"/>
-      <c r="I29" s="174"/>
-      <c r="J29" s="174"/>
-      <c r="K29" s="174"/>
-      <c r="L29" s="174"/>
-      <c r="M29" s="174"/>
-      <c r="N29" s="174"/>
-      <c r="O29" s="174"/>
+      <c r="D29" s="164"/>
+      <c r="E29" s="164"/>
+      <c r="F29" s="164"/>
+      <c r="G29" s="164"/>
+      <c r="H29" s="164"/>
+      <c r="I29" s="164"/>
+      <c r="J29" s="164"/>
+      <c r="K29" s="164"/>
+      <c r="L29" s="164"/>
+      <c r="M29" s="164"/>
+      <c r="N29" s="164"/>
+      <c r="O29" s="164"/>
     </row>
     <row r="30" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D30" s="174"/>
-      <c r="E30" s="174"/>
-      <c r="F30" s="174"/>
-      <c r="G30" s="174"/>
-      <c r="H30" s="174"/>
-      <c r="I30" s="174"/>
-      <c r="J30" s="174"/>
-      <c r="K30" s="174"/>
-      <c r="L30" s="174"/>
-      <c r="M30" s="174"/>
-      <c r="N30" s="174"/>
-      <c r="O30" s="174"/>
+      <c r="D30" s="164"/>
+      <c r="E30" s="164"/>
+      <c r="F30" s="164"/>
+      <c r="G30" s="164"/>
+      <c r="H30" s="164"/>
+      <c r="I30" s="164"/>
+      <c r="J30" s="164"/>
+      <c r="K30" s="164"/>
+      <c r="L30" s="164"/>
+      <c r="M30" s="164"/>
+      <c r="N30" s="164"/>
+      <c r="O30" s="164"/>
     </row>
     <row r="31" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D31" s="174"/>
-      <c r="E31" s="174"/>
-      <c r="F31" s="174"/>
-      <c r="G31" s="174"/>
-      <c r="H31" s="174"/>
-      <c r="I31" s="174"/>
-      <c r="J31" s="174"/>
-      <c r="K31" s="174"/>
-      <c r="L31" s="174"/>
-      <c r="M31" s="174"/>
-      <c r="N31" s="174"/>
-      <c r="O31" s="174"/>
+      <c r="D31" s="164"/>
+      <c r="E31" s="164"/>
+      <c r="F31" s="164"/>
+      <c r="G31" s="164"/>
+      <c r="H31" s="164"/>
+      <c r="I31" s="164"/>
+      <c r="J31" s="164"/>
+      <c r="K31" s="164"/>
+      <c r="L31" s="164"/>
+      <c r="M31" s="164"/>
+      <c r="N31" s="164"/>
+      <c r="O31" s="164"/>
     </row>
     <row r="32" spans="1:21" ht="65.25" customHeight="1">
-      <c r="D32" s="174"/>
-      <c r="E32" s="174"/>
-      <c r="F32" s="174"/>
-      <c r="G32" s="174"/>
-      <c r="H32" s="174"/>
-      <c r="I32" s="174"/>
-      <c r="J32" s="174"/>
-      <c r="K32" s="174"/>
-      <c r="L32" s="174"/>
-      <c r="M32" s="174"/>
-      <c r="N32" s="174"/>
-      <c r="O32" s="174"/>
+      <c r="D32" s="164"/>
+      <c r="E32" s="164"/>
+      <c r="F32" s="164"/>
+      <c r="G32" s="164"/>
+      <c r="H32" s="164"/>
+      <c r="I32" s="164"/>
+      <c r="J32" s="164"/>
+      <c r="K32" s="164"/>
+      <c r="L32" s="164"/>
+      <c r="M32" s="164"/>
+      <c r="N32" s="164"/>
+      <c r="O32" s="164"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="F5:F6"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P5:P6"/>
     <mergeCell ref="D27:O32"/>
@@ -4483,11 +4494,6 @@
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="B4:P4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="F5:F6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" orientation="landscape" r:id="rId1"/>
@@ -4500,7 +4506,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="3" spans="3:3">
-      <c r="C3" s="147" t="s">
+      <c r="C3" s="141" t="s">
         <v>118</v>
       </c>
     </row>

--- a/2026/BELTRAN 34/Agosto/Agosto BELTRAN.xlsx
+++ b/2026/BELTRAN 34/Agosto/Agosto BELTRAN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BELTRAN 34\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{194BC290-6F03-4F6D-A6B9-40857D8D3308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFFC7C15-0EFB-441D-96C8-8B0736F64F2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$33</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$93</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$94</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="133">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -393,49 +393,46 @@
     <t>$157.200 transfririo el 1° C. + Cochera C</t>
   </si>
   <si>
-    <t>Articulos de limpieza</t>
-  </si>
-  <si>
     <t>Subido en Juli0 a $91.000</t>
   </si>
   <si>
-    <t>VTO 17/09</t>
-  </si>
-  <si>
-    <t>Transf 05/08</t>
-  </si>
-  <si>
-    <t>Transf 12/08</t>
-  </si>
-  <si>
-    <t>Celestino Soledad - Servicio de limpieza - Mes de Julio (tomo vacaciones) y Agosto</t>
-  </si>
-  <si>
-    <t>Transf 28/08</t>
-  </si>
-  <si>
-    <t>Agosto</t>
-  </si>
-  <si>
-    <t>Julio</t>
-  </si>
-  <si>
     <t>Federacion patronal - Seguro integral de consorcio</t>
   </si>
   <si>
-    <t>Debito 28/08</t>
-  </si>
-  <si>
-    <t>Honorarios administracion -  JULIO Y AGOSTO</t>
-  </si>
-  <si>
-    <t>Transf 30/08</t>
-  </si>
-  <si>
     <t>Seguro - Sra. Soledad - La Holando - Poliza nro. 690173-2</t>
   </si>
   <si>
     <t>Hay una diferencia de caja correspondiente a un gasto de AYSA a solucionar en S3ptiembr3</t>
+  </si>
+  <si>
+    <t>VTO 16/10</t>
+  </si>
+  <si>
+    <t>Transf 07/09</t>
+  </si>
+  <si>
+    <t>Gasto particular: Desglose deuda para presentar en juzgado</t>
+  </si>
+  <si>
+    <t>Kromacolor pinturerias - Compra de recuplast, venda y rodillos para trabajo en terraza</t>
+  </si>
+  <si>
+    <t>Transf 16/09</t>
+  </si>
+  <si>
+    <t>Adelanto Mano de obra - Sr. Facundo Heredia</t>
+  </si>
+  <si>
+    <t>Transf  23/09</t>
+  </si>
+  <si>
+    <t>Debito 28/09</t>
+  </si>
+  <si>
+    <t>Honorarios administracion -  Se adeuda Septiembre</t>
+  </si>
+  <si>
+    <t>Celestino Soledad - Servicio de limpieza - No se abona por falta de fondos</t>
   </si>
 </sst>
 </file>
@@ -1474,7 +1471,7 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="35" applyProtection="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="36" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="185">
+  <cellXfs count="188">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1673,6 +1670,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1682,6 +1683,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1709,6 +1713,24 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1724,9 +1746,6 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1757,27 +1776,12 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Énfasis1 2" xfId="4" xr:uid="{E13FD6FD-4381-40A3-9669-15D4AFB54255}"/>
@@ -2207,7 +2211,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L93"/>
+  <dimension ref="A1:L94"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="37.5703125" customWidth="1"/>
@@ -2245,41 +2249,41 @@
       <c r="D3" s="71"/>
     </row>
     <row r="4" spans="1:4" ht="32.25" customHeight="1">
-      <c r="A4" s="148" t="s">
+      <c r="A4" s="150" t="s">
         <v>103</v>
       </c>
-      <c r="B4" s="148"/>
+      <c r="B4" s="150"/>
       <c r="C4" s="72"/>
       <c r="D4" s="72"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="148"/>
-      <c r="B5" s="148"/>
+      <c r="A5" s="150"/>
+      <c r="B5" s="150"/>
       <c r="C5" s="72"/>
       <c r="D5" s="72"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="148"/>
-      <c r="B6" s="148"/>
+      <c r="A6" s="150"/>
+      <c r="B6" s="150"/>
       <c r="C6" s="72"/>
       <c r="D6" s="72"/>
     </row>
     <row r="7" spans="1:4" ht="13.5" customHeight="1">
-      <c r="A7" s="148"/>
-      <c r="B7" s="148"/>
+      <c r="A7" s="150"/>
+      <c r="B7" s="150"/>
       <c r="C7" s="72"/>
       <c r="D7" s="72"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="B9" s="155" t="s">
-        <v>121</v>
+      <c r="B9" s="158" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="B10" s="155"/>
+      <c r="B10" s="158"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="B11" s="155"/>
+      <c r="B11" s="158"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="62"/>
@@ -2294,30 +2298,30 @@
       <c r="D13" s="62"/>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1">
-      <c r="A14" s="179" t="s">
+      <c r="A14" s="153" t="s">
         <v>96</v>
       </c>
-      <c r="B14" s="179"/>
-      <c r="C14" s="179"/>
-      <c r="D14" s="179"/>
+      <c r="B14" s="153"/>
+      <c r="C14" s="153"/>
+      <c r="D14" s="153"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1">
-      <c r="A15" s="179"/>
-      <c r="B15" s="179"/>
-      <c r="C15" s="179"/>
-      <c r="D15" s="179"/>
+      <c r="A15" s="153"/>
+      <c r="B15" s="153"/>
+      <c r="C15" s="153"/>
+      <c r="D15" s="153"/>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1">
-      <c r="A16" s="179"/>
-      <c r="B16" s="179"/>
-      <c r="C16" s="179"/>
-      <c r="D16" s="179"/>
+      <c r="A16" s="153"/>
+      <c r="B16" s="153"/>
+      <c r="C16" s="153"/>
+      <c r="D16" s="153"/>
     </row>
     <row r="17" spans="1:7" ht="53.25" customHeight="1">
-      <c r="A17" s="179"/>
-      <c r="B17" s="179"/>
-      <c r="C17" s="179"/>
-      <c r="D17" s="179"/>
+      <c r="A17" s="153"/>
+      <c r="B17" s="153"/>
+      <c r="C17" s="153"/>
+      <c r="D17" s="153"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1">
       <c r="A18" s="62"/>
@@ -2326,7 +2330,7 @@
       <c r="D18" s="62"/>
     </row>
     <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1">
-      <c r="A19" s="180"/>
+      <c r="A19" s="149"/>
       <c r="B19" s="62"/>
       <c r="C19" s="62"/>
       <c r="D19" s="62"/>
@@ -2355,19 +2359,19 @@
       <c r="G22" s="16"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A23" s="156" t="s">
-        <v>124</v>
-      </c>
-      <c r="B23" s="157"/>
-      <c r="C23" s="181">
-        <v>450000</v>
+      <c r="A23" s="159" t="s">
+        <v>132</v>
+      </c>
+      <c r="B23" s="160"/>
+      <c r="C23" s="163">
+        <v>0</v>
       </c>
       <c r="D23" s="48"/>
     </row>
     <row r="24" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A24" s="158"/>
-      <c r="B24" s="159"/>
-      <c r="C24" s="182"/>
+      <c r="A24" s="161"/>
+      <c r="B24" s="162"/>
+      <c r="C24" s="164"/>
       <c r="D24" s="48"/>
     </row>
     <row r="25" spans="1:7">
@@ -2377,7 +2381,7 @@
       <c r="B25" s="111"/>
       <c r="C25" s="142">
         <f>SUM(C23:C24)</f>
-        <v>450000</v>
+        <v>0</v>
       </c>
       <c r="D25" s="49"/>
     </row>
@@ -2424,7 +2428,7 @@
       <c r="C31" s="5"/>
       <c r="D31" s="50">
         <f>C25+C30</f>
-        <v>450000</v>
+        <v>0</v>
       </c>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
@@ -2440,18 +2444,15 @@
     </row>
     <row r="33" spans="1:7" ht="22.5" customHeight="1">
       <c r="A33" s="97" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B33" s="113"/>
       <c r="C33" s="84">
-        <f>91000*2</f>
-        <v>182000</v>
-      </c>
-      <c r="D33" s="82" t="s">
-        <v>131</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D33" s="82"/>
       <c r="F33" s="16" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G33" s="4"/>
     </row>
@@ -2463,7 +2464,7 @@
       <c r="C34" s="143"/>
       <c r="D34" s="50">
         <f>SUM(C33:C33)</f>
-        <v>182000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="16.5" customHeight="1">
@@ -2475,27 +2476,27 @@
       <c r="D35" s="27"/>
     </row>
     <row r="36" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A36" s="149" t="s">
-        <v>128</v>
-      </c>
-      <c r="B36" s="150"/>
-      <c r="C36" s="183">
+      <c r="A36" s="151" t="s">
+        <v>120</v>
+      </c>
+      <c r="B36" s="152"/>
+      <c r="C36" s="186">
         <v>89533</v>
       </c>
       <c r="D36" s="81" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="22.5" customHeight="1">
       <c r="A37" s="146" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="B37" s="147"/>
-      <c r="C37" s="184">
+      <c r="C37" s="187">
         <v>5587.48</v>
       </c>
       <c r="D37" s="81" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15.75" thickBot="1">
@@ -2582,11 +2583,11 @@
         <v>94</v>
       </c>
       <c r="B46" s="48"/>
-      <c r="C46" s="87">
-        <v>86429.79</v>
+      <c r="C46" s="184">
+        <v>66626.53</v>
       </c>
       <c r="D46" s="79" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="14.25" customHeight="1">
@@ -2594,11 +2595,11 @@
         <v>95</v>
       </c>
       <c r="B47" s="48"/>
-      <c r="C47" s="87">
-        <v>392672.62</v>
+      <c r="C47" s="184">
+        <v>502776.73</v>
       </c>
       <c r="D47" s="79" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F47" t="s">
         <v>116</v>
@@ -2612,7 +2613,7 @@
       <c r="C48" s="13"/>
       <c r="D48" s="52">
         <f>SUM(C46:C47)</f>
-        <v>479102.41</v>
+        <v>569403.26</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" thickBot="1">
@@ -2624,43 +2625,39 @@
       <c r="D49" s="55"/>
     </row>
     <row r="50" spans="1:6" ht="19.899999999999999" customHeight="1">
-      <c r="A50" s="149" t="s">
+      <c r="A50" s="151" t="s">
         <v>110</v>
       </c>
-      <c r="B50" s="150"/>
-      <c r="C50" s="87">
+      <c r="B50" s="152"/>
+      <c r="C50" s="184">
         <v>126000</v>
       </c>
-      <c r="D50" s="77" t="s">
-        <v>123</v>
+      <c r="D50" s="79" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="19.899999999999999" customHeight="1">
       <c r="A51" s="146" t="s">
-        <v>119</v>
-      </c>
-      <c r="B51" s="147" t="s">
+        <v>128</v>
+      </c>
+      <c r="B51" s="148"/>
+      <c r="C51" s="184">
+        <v>300000</v>
+      </c>
+      <c r="D51" s="77" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="41.25" customHeight="1">
+      <c r="A52" s="151" t="s">
         <v>126</v>
       </c>
-      <c r="C51" s="87">
-        <v>29400</v>
-      </c>
-      <c r="D51" s="77" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="19.899999999999999" customHeight="1">
-      <c r="A52" s="146" t="s">
-        <v>119</v>
-      </c>
-      <c r="B52" s="147" t="s">
+      <c r="B52" s="152"/>
+      <c r="C52" s="184">
+        <v>580730.54</v>
+      </c>
+      <c r="D52" s="77" t="s">
         <v>127</v>
-      </c>
-      <c r="C52" s="87">
-        <v>37600</v>
-      </c>
-      <c r="D52" s="77" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.75" thickBot="1">
@@ -2671,7 +2668,7 @@
       <c r="C53" s="8"/>
       <c r="D53" s="57">
         <f>SUM(C50:C52)</f>
-        <v>193000</v>
+        <v>1006730.54</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="15.75" thickBot="1">
@@ -2687,7 +2684,7 @@
         <v>117</v>
       </c>
       <c r="B55" s="48"/>
-      <c r="C55" s="87">
+      <c r="C55" s="184">
         <v>69000</v>
       </c>
       <c r="D55" s="58"/>
@@ -2697,8 +2694,8 @@
         <v>102</v>
       </c>
       <c r="B56" s="48"/>
-      <c r="C56" s="87">
-        <v>40355.57</v>
+      <c r="C56" s="184">
+        <v>39863.769999999997</v>
       </c>
       <c r="D56" s="56"/>
     </row>
@@ -2710,7 +2707,7 @@
       <c r="C57" s="59"/>
       <c r="D57" s="52">
         <f>SUM(C55:C56)</f>
-        <v>109355.57</v>
+        <v>108863.76999999999</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="15.75" thickBot="1">
@@ -2720,11 +2717,11 @@
       <c r="D58" s="60"/>
     </row>
     <row r="59" spans="1:6" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A59" s="152" t="s">
+      <c r="A59" s="155" t="s">
         <v>114</v>
       </c>
-      <c r="B59" s="153"/>
-      <c r="C59" s="154"/>
+      <c r="B59" s="156"/>
+      <c r="C59" s="157"/>
       <c r="D59" s="61">
         <v>0</v>
       </c>
@@ -2744,7 +2741,7 @@
       <c r="C61" s="64"/>
       <c r="D61" s="65">
         <f>(SUM(D26:D59))</f>
-        <v>1508578.46</v>
+        <v>1780118.05</v>
       </c>
       <c r="E61" s="18"/>
       <c r="F61" s="18"/>
@@ -2834,7 +2831,7 @@
       </c>
       <c r="B73" s="131">
         <f>D61</f>
-        <v>1508578.46</v>
+        <v>1780118.05</v>
       </c>
       <c r="C73" s="132"/>
     </row>
@@ -2844,7 +2841,7 @@
       </c>
       <c r="B74" s="131">
         <f>D61-D59</f>
-        <v>1508578.46</v>
+        <v>1780118.05</v>
       </c>
       <c r="C74" s="62"/>
     </row>
@@ -2917,90 +2914,100 @@
         <v>54</v>
       </c>
       <c r="B83" s="56">
-        <f>B92</f>
+        <f>B93</f>
         <v>0</v>
       </c>
       <c r="C83" s="62"/>
       <c r="F83" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12">
-      <c r="A84" s="138" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="39.75" customHeight="1">
+      <c r="A84" s="185" t="s">
+        <v>125</v>
+      </c>
+      <c r="B84" s="144">
+        <v>-50000</v>
+      </c>
+      <c r="C84" s="62"/>
+    </row>
+    <row r="85" spans="1:12">
+      <c r="A85" s="138" t="s">
         <v>38</v>
       </c>
-      <c r="B84" s="144">
+      <c r="B85" s="144">
         <f>-B74</f>
-        <v>-1508578.46</v>
-      </c>
-      <c r="C84" s="62"/>
-    </row>
-    <row r="85" spans="1:12">
-      <c r="A85" s="137" t="s">
+        <v>-1780118.05</v>
+      </c>
+      <c r="C85" s="62"/>
+    </row>
+    <row r="86" spans="1:12">
+      <c r="A86" s="137" t="s">
         <v>39</v>
       </c>
-      <c r="B85" s="56">
+      <c r="B86" s="56">
         <f>-(B75)</f>
         <v>0</v>
       </c>
-      <c r="C85" s="62"/>
-    </row>
-    <row r="86" spans="1:12">
-      <c r="A86" s="6" t="s">
+      <c r="C86" s="62"/>
+    </row>
+    <row r="87" spans="1:12">
+      <c r="A87" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B86" s="98">
-        <f>SUM(B81:B85)</f>
-        <v>1003717.6899999995</v>
-      </c>
-      <c r="C86" s="123"/>
-    </row>
-    <row r="87" spans="1:12" ht="34.5" customHeight="1">
-      <c r="B87" s="16"/>
-      <c r="C87" s="18"/>
-      <c r="D87" s="123"/>
-    </row>
-    <row r="88" spans="1:12">
-      <c r="A88" s="151" t="s">
+      <c r="B87" s="98">
+        <f>SUM(B81:B86)</f>
+        <v>682178.09999999939</v>
+      </c>
+      <c r="C87" s="123"/>
+    </row>
+    <row r="88" spans="1:12" ht="34.5" customHeight="1">
+      <c r="B88" s="16"/>
+      <c r="C88" s="18"/>
+      <c r="D88" s="123"/>
+    </row>
+    <row r="89" spans="1:12">
+      <c r="A89" s="154" t="s">
         <v>46</v>
       </c>
-      <c r="B88" s="151"/>
-    </row>
-    <row r="89" spans="1:12" ht="27.75" customHeight="1">
-      <c r="A89" s="151"/>
-      <c r="B89" s="151"/>
-    </row>
-    <row r="90" spans="1:12" ht="32.25" customHeight="1">
-      <c r="A90" s="68"/>
-      <c r="B90" s="12"/>
+      <c r="B89" s="154"/>
+    </row>
+    <row r="90" spans="1:12" ht="27.75" customHeight="1">
+      <c r="A90" s="154"/>
+      <c r="B90" s="154"/>
     </row>
     <row r="91" spans="1:12" ht="32.25" customHeight="1">
       <c r="A91" s="68"/>
       <c r="B91" s="12"/>
     </row>
-    <row r="92" spans="1:12">
-      <c r="A92" s="19" t="s">
+    <row r="92" spans="1:12" ht="32.25" customHeight="1">
+      <c r="A92" s="68"/>
+      <c r="B92" s="12"/>
+    </row>
+    <row r="93" spans="1:12">
+      <c r="A93" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B92" s="69">
-        <f>SUM(B90:B91)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12">
-      <c r="L93" s="3"/>
+      <c r="B93" s="69">
+        <f>SUM(B91:B92)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12">
+      <c r="L94" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A4:B7"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A14:D17"/>
-    <mergeCell ref="A88:B89"/>
+    <mergeCell ref="A89:B90"/>
     <mergeCell ref="A59:C59"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="A23:B24"/>
     <mergeCell ref="C23:C24"/>
+    <mergeCell ref="A52:B52"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3037,22 +3044,22 @@
   <sheetData>
     <row r="1" spans="1:21" ht="12.95" customHeight="1">
       <c r="A1" s="99"/>
-      <c r="B1" s="160" t="str">
+      <c r="B1" s="169" t="str">
         <f>RESUMEN!A4</f>
         <v xml:space="preserve">Titular: CONSORCIO DE PROPIETARIOS CORONEL BELTRAN 34
 Banco Santander: Cta Corriente en Pesos 533-030591/4
 Cuit del consorcio: 30-71897608-8
 CBU: 0720533020000003059140 - Alias: SALMON.ARMADA.FOCO                                                                                                                                                                                                                                                                                                      </v>
       </c>
-      <c r="C1" s="160"/>
-      <c r="D1" s="160"/>
-      <c r="E1" s="160"/>
-      <c r="F1" s="160"/>
-      <c r="G1" s="160"/>
-      <c r="H1" s="160"/>
-      <c r="I1" s="160"/>
-      <c r="J1" s="160"/>
-      <c r="K1" s="160"/>
+      <c r="C1" s="169"/>
+      <c r="D1" s="169"/>
+      <c r="E1" s="169"/>
+      <c r="F1" s="169"/>
+      <c r="G1" s="169"/>
+      <c r="H1" s="169"/>
+      <c r="I1" s="169"/>
+      <c r="J1" s="169"/>
+      <c r="K1" s="169"/>
       <c r="L1" s="100"/>
       <c r="M1" s="100"/>
       <c r="N1" s="100"/>
@@ -3061,16 +3068,16 @@
     </row>
     <row r="2" spans="1:21" ht="33.75" customHeight="1">
       <c r="A2" s="102"/>
-      <c r="B2" s="161"/>
-      <c r="C2" s="161"/>
-      <c r="D2" s="161"/>
-      <c r="E2" s="161"/>
-      <c r="F2" s="161"/>
-      <c r="G2" s="161"/>
-      <c r="H2" s="161"/>
-      <c r="I2" s="161"/>
-      <c r="J2" s="161"/>
-      <c r="K2" s="161"/>
+      <c r="B2" s="170"/>
+      <c r="C2" s="170"/>
+      <c r="D2" s="170"/>
+      <c r="E2" s="170"/>
+      <c r="F2" s="170"/>
+      <c r="G2" s="170"/>
+      <c r="H2" s="170"/>
+      <c r="I2" s="170"/>
+      <c r="J2" s="170"/>
+      <c r="K2" s="170"/>
       <c r="L2" s="103"/>
       <c r="M2" s="103" t="s">
         <v>4</v>
@@ -3087,16 +3094,16 @@
     </row>
     <row r="3" spans="1:21" ht="46.5" customHeight="1" thickBot="1">
       <c r="A3" s="105"/>
-      <c r="B3" s="162"/>
-      <c r="C3" s="162"/>
-      <c r="D3" s="162"/>
-      <c r="E3" s="162"/>
-      <c r="F3" s="162"/>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="162"/>
-      <c r="K3" s="162"/>
+      <c r="B3" s="171"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="171"/>
+      <c r="G3" s="171"/>
+      <c r="H3" s="171"/>
+      <c r="I3" s="171"/>
+      <c r="J3" s="171"/>
+      <c r="K3" s="171"/>
       <c r="L3" s="106"/>
       <c r="M3" s="106" t="s">
         <v>56</v>
@@ -3109,96 +3116,96 @@
     </row>
     <row r="4" spans="1:21" ht="30.6" customHeight="1" thickBot="1">
       <c r="A4" s="2"/>
-      <c r="B4" s="173" t="s">
+      <c r="B4" s="181" t="s">
         <v>97</v>
       </c>
-      <c r="C4" s="174"/>
-      <c r="D4" s="174"/>
-      <c r="E4" s="174"/>
-      <c r="F4" s="174"/>
-      <c r="G4" s="174"/>
-      <c r="H4" s="174"/>
-      <c r="I4" s="174"/>
-      <c r="J4" s="174"/>
-      <c r="K4" s="174"/>
-      <c r="L4" s="174"/>
-      <c r="M4" s="174"/>
-      <c r="N4" s="174"/>
-      <c r="O4" s="174"/>
-      <c r="P4" s="175"/>
+      <c r="C4" s="182"/>
+      <c r="D4" s="182"/>
+      <c r="E4" s="182"/>
+      <c r="F4" s="182"/>
+      <c r="G4" s="182"/>
+      <c r="H4" s="182"/>
+      <c r="I4" s="182"/>
+      <c r="J4" s="182"/>
+      <c r="K4" s="182"/>
+      <c r="L4" s="182"/>
+      <c r="M4" s="182"/>
+      <c r="N4" s="182"/>
+      <c r="O4" s="182"/>
+      <c r="P4" s="183"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="176" t="s">
+      <c r="A5" s="165" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="178" t="s">
+      <c r="B5" s="167" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="165" t="s">
+      <c r="C5" s="168" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="165" t="s">
+      <c r="D5" s="168" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="165" t="s">
+      <c r="E5" s="168" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="165" t="s">
+      <c r="F5" s="168" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="165" t="s">
+      <c r="G5" s="168" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="165" t="s">
+      <c r="H5" s="168" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="165" t="s">
+      <c r="I5" s="168" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="169" t="s">
+      <c r="J5" s="177" t="s">
         <v>44</v>
       </c>
-      <c r="K5" s="167" t="s">
+      <c r="K5" s="175" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="167" t="s">
+      <c r="L5" s="175" t="s">
         <v>10</v>
       </c>
-      <c r="M5" s="167" t="s">
+      <c r="M5" s="175" t="s">
         <v>40</v>
       </c>
-      <c r="N5" s="171" t="s">
+      <c r="N5" s="179" t="s">
         <v>51</v>
       </c>
       <c r="O5" s="88" t="s">
         <v>50</v>
       </c>
-      <c r="P5" s="163" t="s">
+      <c r="P5" s="172" t="s">
         <v>49</v>
       </c>
       <c r="S5" s="18"/>
       <c r="T5" s="16"/>
     </row>
     <row r="6" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A6" s="177"/>
-      <c r="B6" s="178"/>
-      <c r="C6" s="165"/>
-      <c r="D6" s="165"/>
-      <c r="E6" s="166"/>
-      <c r="F6" s="165"/>
-      <c r="G6" s="165"/>
-      <c r="H6" s="165"/>
-      <c r="I6" s="166"/>
-      <c r="J6" s="170"/>
-      <c r="K6" s="168"/>
-      <c r="L6" s="167"/>
-      <c r="M6" s="168"/>
-      <c r="N6" s="172"/>
+      <c r="A6" s="166"/>
+      <c r="B6" s="167"/>
+      <c r="C6" s="168"/>
+      <c r="D6" s="168"/>
+      <c r="E6" s="174"/>
+      <c r="F6" s="168"/>
+      <c r="G6" s="168"/>
+      <c r="H6" s="168"/>
+      <c r="I6" s="174"/>
+      <c r="J6" s="178"/>
+      <c r="K6" s="176"/>
+      <c r="L6" s="175"/>
+      <c r="M6" s="176"/>
+      <c r="N6" s="180"/>
       <c r="O6" s="23" t="str">
         <f>RESUMEN!B9</f>
-        <v>VTO 17/09</v>
-      </c>
-      <c r="P6" s="163"/>
+        <v>VTO 16/10</v>
+      </c>
+      <c r="P6" s="172"/>
       <c r="S6" s="16">
         <v>65160</v>
       </c>
@@ -4388,99 +4395,94 @@
     </row>
     <row r="26" spans="1:21" ht="15" hidden="1" customHeight="1"/>
     <row r="27" spans="1:21" ht="15" customHeight="1">
-      <c r="D27" s="164" t="s">
+      <c r="D27" s="173" t="s">
         <v>63</v>
       </c>
-      <c r="E27" s="164"/>
-      <c r="F27" s="164"/>
-      <c r="G27" s="164"/>
-      <c r="H27" s="164"/>
-      <c r="I27" s="164"/>
-      <c r="J27" s="164"/>
-      <c r="K27" s="164"/>
-      <c r="L27" s="164"/>
-      <c r="M27" s="164"/>
-      <c r="N27" s="164"/>
-      <c r="O27" s="164"/>
+      <c r="E27" s="173"/>
+      <c r="F27" s="173"/>
+      <c r="G27" s="173"/>
+      <c r="H27" s="173"/>
+      <c r="I27" s="173"/>
+      <c r="J27" s="173"/>
+      <c r="K27" s="173"/>
+      <c r="L27" s="173"/>
+      <c r="M27" s="173"/>
+      <c r="N27" s="173"/>
+      <c r="O27" s="173"/>
       <c r="S27" s="16"/>
     </row>
     <row r="28" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D28" s="164"/>
-      <c r="E28" s="164"/>
-      <c r="F28" s="164"/>
-      <c r="G28" s="164"/>
-      <c r="H28" s="164"/>
-      <c r="I28" s="164"/>
-      <c r="J28" s="164"/>
-      <c r="K28" s="164"/>
-      <c r="L28" s="164"/>
-      <c r="M28" s="164"/>
-      <c r="N28" s="164"/>
-      <c r="O28" s="164"/>
+      <c r="D28" s="173"/>
+      <c r="E28" s="173"/>
+      <c r="F28" s="173"/>
+      <c r="G28" s="173"/>
+      <c r="H28" s="173"/>
+      <c r="I28" s="173"/>
+      <c r="J28" s="173"/>
+      <c r="K28" s="173"/>
+      <c r="L28" s="173"/>
+      <c r="M28" s="173"/>
+      <c r="N28" s="173"/>
+      <c r="O28" s="173"/>
     </row>
     <row r="29" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D29" s="164"/>
-      <c r="E29" s="164"/>
-      <c r="F29" s="164"/>
-      <c r="G29" s="164"/>
-      <c r="H29" s="164"/>
-      <c r="I29" s="164"/>
-      <c r="J29" s="164"/>
-      <c r="K29" s="164"/>
-      <c r="L29" s="164"/>
-      <c r="M29" s="164"/>
-      <c r="N29" s="164"/>
-      <c r="O29" s="164"/>
+      <c r="D29" s="173"/>
+      <c r="E29" s="173"/>
+      <c r="F29" s="173"/>
+      <c r="G29" s="173"/>
+      <c r="H29" s="173"/>
+      <c r="I29" s="173"/>
+      <c r="J29" s="173"/>
+      <c r="K29" s="173"/>
+      <c r="L29" s="173"/>
+      <c r="M29" s="173"/>
+      <c r="N29" s="173"/>
+      <c r="O29" s="173"/>
     </row>
     <row r="30" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D30" s="164"/>
-      <c r="E30" s="164"/>
-      <c r="F30" s="164"/>
-      <c r="G30" s="164"/>
-      <c r="H30" s="164"/>
-      <c r="I30" s="164"/>
-      <c r="J30" s="164"/>
-      <c r="K30" s="164"/>
-      <c r="L30" s="164"/>
-      <c r="M30" s="164"/>
-      <c r="N30" s="164"/>
-      <c r="O30" s="164"/>
+      <c r="D30" s="173"/>
+      <c r="E30" s="173"/>
+      <c r="F30" s="173"/>
+      <c r="G30" s="173"/>
+      <c r="H30" s="173"/>
+      <c r="I30" s="173"/>
+      <c r="J30" s="173"/>
+      <c r="K30" s="173"/>
+      <c r="L30" s="173"/>
+      <c r="M30" s="173"/>
+      <c r="N30" s="173"/>
+      <c r="O30" s="173"/>
     </row>
     <row r="31" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D31" s="164"/>
-      <c r="E31" s="164"/>
-      <c r="F31" s="164"/>
-      <c r="G31" s="164"/>
-      <c r="H31" s="164"/>
-      <c r="I31" s="164"/>
-      <c r="J31" s="164"/>
-      <c r="K31" s="164"/>
-      <c r="L31" s="164"/>
-      <c r="M31" s="164"/>
-      <c r="N31" s="164"/>
-      <c r="O31" s="164"/>
+      <c r="D31" s="173"/>
+      <c r="E31" s="173"/>
+      <c r="F31" s="173"/>
+      <c r="G31" s="173"/>
+      <c r="H31" s="173"/>
+      <c r="I31" s="173"/>
+      <c r="J31" s="173"/>
+      <c r="K31" s="173"/>
+      <c r="L31" s="173"/>
+      <c r="M31" s="173"/>
+      <c r="N31" s="173"/>
+      <c r="O31" s="173"/>
     </row>
     <row r="32" spans="1:21" ht="65.25" customHeight="1">
-      <c r="D32" s="164"/>
-      <c r="E32" s="164"/>
-      <c r="F32" s="164"/>
-      <c r="G32" s="164"/>
-      <c r="H32" s="164"/>
-      <c r="I32" s="164"/>
-      <c r="J32" s="164"/>
-      <c r="K32" s="164"/>
-      <c r="L32" s="164"/>
-      <c r="M32" s="164"/>
-      <c r="N32" s="164"/>
-      <c r="O32" s="164"/>
+      <c r="D32" s="173"/>
+      <c r="E32" s="173"/>
+      <c r="F32" s="173"/>
+      <c r="G32" s="173"/>
+      <c r="H32" s="173"/>
+      <c r="I32" s="173"/>
+      <c r="J32" s="173"/>
+      <c r="K32" s="173"/>
+      <c r="L32" s="173"/>
+      <c r="M32" s="173"/>
+      <c r="N32" s="173"/>
+      <c r="O32" s="173"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="F5:F6"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P5:P6"/>
     <mergeCell ref="D27:O32"/>
@@ -4494,6 +4496,11 @@
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="B4:P4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="F5:F6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" orientation="landscape" r:id="rId1"/>
